--- a/informes_data/ACB/2025-26/playoffs/individual/NP_play_by_play_105353_W2.xlsx
+++ b/informes_data/ACB/2025-26/playoffs/individual/NP_play_by_play_105353_W2.xlsx
@@ -570,64 +570,64 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>10.3715</v>
+        <v>10.4671</v>
       </c>
       <c r="E2" t="n">
-        <v>8.897</v>
+        <v>9.0585</v>
       </c>
       <c r="F2" t="n">
-        <v>1.4746</v>
+        <v>1.4086</v>
       </c>
       <c r="G2" t="n">
-        <v>7.3684</v>
+        <v>7.4909</v>
       </c>
       <c r="H2" t="n">
-        <v>-1.9287</v>
+        <v>-1.8021</v>
       </c>
       <c r="I2" t="n">
-        <v>9.2971</v>
+        <v>9.292999999999999</v>
       </c>
       <c r="J2" t="n">
-        <v>7.4717</v>
+        <v>7.7943</v>
       </c>
       <c r="K2" t="n">
-        <v>-2.2554</v>
+        <v>-2.0374</v>
       </c>
       <c r="L2" t="n">
-        <v>9.727</v>
+        <v>9.8317</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.1033</v>
+        <v>-0.3035</v>
       </c>
       <c r="N2" t="n">
-        <v>0.3267</v>
+        <v>0.2352</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.43</v>
+        <v>-0.5387</v>
       </c>
       <c r="P2" t="n">
-        <v>1.1538</v>
+        <v>1.1475</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.1538</v>
+        <v>-1.1475</v>
       </c>
       <c r="R2" t="n">
-        <v>2.3075</v>
+        <v>2.295</v>
       </c>
       <c r="S2" t="n">
-        <v>0.6262</v>
+        <v>0.5959</v>
       </c>
       <c r="T2" t="n">
-        <v>1.3559</v>
+        <v>1.1788</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.7297</v>
+        <v>-0.5829</v>
       </c>
       <c r="V2" t="n">
-        <v>1.2232</v>
+        <v>1.2329</v>
       </c>
       <c r="W2" t="n">
-        <v>1.2232</v>
+        <v>1.2329</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
@@ -653,64 +653,64 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.9047</v>
+        <v>3.9023</v>
       </c>
       <c r="E3" t="n">
-        <v>0.8433</v>
+        <v>0.8885999999999999</v>
       </c>
       <c r="F3" t="n">
-        <v>3.0614</v>
+        <v>3.0137</v>
       </c>
       <c r="G3" t="n">
-        <v>1.1391</v>
+        <v>1.1395</v>
       </c>
       <c r="H3" t="n">
-        <v>1.4018</v>
+        <v>1.3887</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.2627</v>
+        <v>-0.2493</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.0356</v>
+        <v>0.1521</v>
       </c>
       <c r="K3" t="n">
-        <v>0.5683</v>
+        <v>0.6508</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.6039</v>
+        <v>-0.4987</v>
       </c>
       <c r="M3" t="n">
-        <v>1.1747</v>
+        <v>0.9874000000000001</v>
       </c>
       <c r="N3" t="n">
-        <v>0.8335</v>
+        <v>0.7379</v>
       </c>
       <c r="O3" t="n">
-        <v>0.3412</v>
+        <v>0.2494</v>
       </c>
       <c r="P3" t="n">
-        <v>1.6153</v>
+        <v>1.6065</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.1538</v>
+        <v>-1.1475</v>
       </c>
       <c r="R3" t="n">
-        <v>2.7691</v>
+        <v>2.7539</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0733</v>
+        <v>0.0743</v>
       </c>
       <c r="T3" t="n">
-        <v>0.9556</v>
+        <v>0.8018999999999999</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.8823</v>
+        <v>-0.7276</v>
       </c>
       <c r="V3" t="n">
-        <v>1.077</v>
+        <v>1.082</v>
       </c>
       <c r="W3" t="n">
-        <v>1.077</v>
+        <v>1.082</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
@@ -736,67 +736,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.3477</v>
+        <v>3.3131</v>
       </c>
       <c r="E4" t="n">
-        <v>1.7381</v>
+        <v>1.7276</v>
       </c>
       <c r="F4" t="n">
-        <v>1.6096</v>
+        <v>1.5855</v>
       </c>
       <c r="G4" t="n">
-        <v>1.2825</v>
+        <v>1.242</v>
       </c>
       <c r="H4" t="n">
-        <v>0.6132</v>
+        <v>0.6491</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6693</v>
+        <v>0.593</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.0961</v>
+        <v>0.0194</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.3915</v>
+        <v>-0.277</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2954</v>
+        <v>0.2964</v>
       </c>
       <c r="M4" t="n">
-        <v>1.3786</v>
+        <v>1.2226</v>
       </c>
       <c r="N4" t="n">
-        <v>1.0047</v>
+        <v>0.9261</v>
       </c>
       <c r="O4" t="n">
-        <v>0.3739</v>
+        <v>0.2966</v>
       </c>
       <c r="P4" t="n">
-        <v>1.846</v>
+        <v>1.836</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.846</v>
+        <v>1.836</v>
       </c>
       <c r="S4" t="n">
-        <v>0.3653</v>
+        <v>0.386</v>
       </c>
       <c r="T4" t="n">
-        <v>1.8342</v>
+        <v>1.7082</v>
       </c>
       <c r="U4" t="n">
-        <v>-1.4688</v>
+        <v>-1.3222</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.1462</v>
+        <v>-0.1509</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.1462</v>
+        <v>-0.1509</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
@@ -819,64 +819,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.0895</v>
+        <v>3.0865</v>
       </c>
       <c r="E5" t="n">
-        <v>2.3037</v>
+        <v>2.3129</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7858000000000001</v>
+        <v>0.7736</v>
       </c>
       <c r="G5" t="n">
-        <v>1.9686</v>
+        <v>1.9564</v>
       </c>
       <c r="H5" t="n">
-        <v>2.5716</v>
+        <v>2.5829</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.6029</v>
+        <v>-0.6264</v>
       </c>
       <c r="J5" t="n">
-        <v>2.0697</v>
+        <v>2.1242</v>
       </c>
       <c r="K5" t="n">
-        <v>2.0697</v>
+        <v>2.1242</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.1011</v>
+        <v>-0.1678</v>
       </c>
       <c r="N5" t="n">
-        <v>0.5019</v>
+        <v>0.4586</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.6029</v>
+        <v>-0.6264</v>
       </c>
       <c r="P5" t="n">
-        <v>1.1538</v>
+        <v>1.1475</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.1538</v>
+        <v>1.1475</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.1791</v>
+        <v>-0.1682</v>
       </c>
       <c r="T5" t="n">
-        <v>0.0878</v>
+        <v>0.0378</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.2669</v>
+        <v>-0.206</v>
       </c>
       <c r="V5" t="n">
-        <v>0.1462</v>
+        <v>0.1509</v>
       </c>
       <c r="W5" t="n">
-        <v>0.1462</v>
+        <v>0.1509</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -902,67 +902,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.9368</v>
+        <v>1.8446</v>
       </c>
       <c r="E6" t="n">
-        <v>0.3172</v>
+        <v>0.2438</v>
       </c>
       <c r="F6" t="n">
-        <v>1.6196</v>
+        <v>1.6009</v>
       </c>
       <c r="G6" t="n">
-        <v>1.1273</v>
+        <v>1.0337</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.2926</v>
+        <v>-0.3339</v>
       </c>
       <c r="I6" t="n">
-        <v>1.42</v>
+        <v>1.3676</v>
       </c>
       <c r="J6" t="n">
-        <v>0.5603</v>
+        <v>0.5988</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.6213</v>
+        <v>-0.5868</v>
       </c>
       <c r="L6" t="n">
-        <v>1.1816</v>
+        <v>1.1856</v>
       </c>
       <c r="M6" t="n">
-        <v>0.5671</v>
+        <v>0.4349</v>
       </c>
       <c r="N6" t="n">
-        <v>0.3287</v>
+        <v>0.2529</v>
       </c>
       <c r="O6" t="n">
-        <v>0.2384</v>
+        <v>0.182</v>
       </c>
       <c r="P6" t="n">
-        <v>0.6923</v>
+        <v>0.6885</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.1538</v>
+        <v>-1.1475</v>
       </c>
       <c r="R6" t="n">
-        <v>1.846</v>
+        <v>1.836</v>
       </c>
       <c r="S6" t="n">
-        <v>1.048</v>
+        <v>1.0536</v>
       </c>
       <c r="T6" t="n">
-        <v>0.7645</v>
+        <v>0.6415</v>
       </c>
       <c r="U6" t="n">
-        <v>0.2835</v>
+        <v>0.412</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.9308</v>
+        <v>-0.9312</v>
       </c>
       <c r="W6" t="n">
-        <v>0.1462</v>
+        <v>0.1509</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.077</v>
+        <v>-1.082</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -985,67 +985,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.7088</v>
+        <v>0.7362</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.0232</v>
+        <v>-1.969</v>
       </c>
       <c r="F7" t="n">
-        <v>2.732</v>
+        <v>2.7052</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.8535</v>
+        <v>-0.8404</v>
       </c>
       <c r="H7" t="n">
-        <v>0.2379</v>
+        <v>0.2475</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.0914</v>
+        <v>-1.088</v>
       </c>
       <c r="J7" t="n">
-        <v>-2.2667</v>
+        <v>-2.1278</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.7687</v>
+        <v>-0.6962</v>
       </c>
       <c r="L7" t="n">
-        <v>-1.498</v>
+        <v>-1.4316</v>
       </c>
       <c r="M7" t="n">
-        <v>1.4133</v>
+        <v>1.2874</v>
       </c>
       <c r="N7" t="n">
-        <v>1.0066</v>
+        <v>0.9437</v>
       </c>
       <c r="O7" t="n">
-        <v>0.4066</v>
+        <v>0.3437</v>
       </c>
       <c r="P7" t="n">
-        <v>1.3845</v>
+        <v>1.377</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.3845</v>
+        <v>1.377</v>
       </c>
       <c r="S7" t="n">
-        <v>0.7163</v>
+        <v>0.7406</v>
       </c>
       <c r="T7" t="n">
-        <v>0.6359</v>
+        <v>0.549</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0804</v>
+        <v>0.1917</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.5385</v>
+        <v>-0.541</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.3923</v>
+        <v>-0.3901</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.1462</v>
+        <v>-0.1509</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1068,58 +1068,58 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6367</v>
+        <v>0.6319</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.7318</v>
+        <v>-0.695</v>
       </c>
       <c r="F8" t="n">
-        <v>1.3685</v>
+        <v>1.3269</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.5459000000000001</v>
+        <v>-0.5104</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.7813</v>
+        <v>-1.6928</v>
       </c>
       <c r="I8" t="n">
-        <v>1.2353</v>
+        <v>1.1824</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.911</v>
+        <v>-0.7276</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.4359</v>
+        <v>-1.29</v>
       </c>
       <c r="L8" t="n">
-        <v>0.5249</v>
+        <v>0.5624</v>
       </c>
       <c r="M8" t="n">
-        <v>0.3651</v>
+        <v>0.2172</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.3454</v>
+        <v>-0.4027</v>
       </c>
       <c r="O8" t="n">
-        <v>0.7105</v>
+        <v>0.6199</v>
       </c>
       <c r="P8" t="n">
-        <v>0.4615</v>
+        <v>0.459</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.1538</v>
+        <v>-1.1475</v>
       </c>
       <c r="R8" t="n">
-        <v>1.6153</v>
+        <v>1.6065</v>
       </c>
       <c r="S8" t="n">
-        <v>0.7211</v>
+        <v>0.6833</v>
       </c>
       <c r="T8" t="n">
-        <v>1.333</v>
+        <v>1.1801</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.6119</v>
+        <v>-0.4968</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1151,67 +1151,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.5193</v>
+        <v>0.537</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.7699</v>
+        <v>-1.7465</v>
       </c>
       <c r="F9" t="n">
-        <v>2.2892</v>
+        <v>2.2835</v>
       </c>
       <c r="G9" t="n">
-        <v>0.6127</v>
+        <v>0.5731000000000001</v>
       </c>
       <c r="H9" t="n">
-        <v>0.8094</v>
+        <v>0.792</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1968</v>
+        <v>-0.2189</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.4949</v>
+        <v>-0.4204</v>
       </c>
       <c r="K9" t="n">
-        <v>0.3095</v>
+        <v>0.351</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.8044</v>
+        <v>-0.7714</v>
       </c>
       <c r="M9" t="n">
-        <v>1.1075</v>
+        <v>0.9935</v>
       </c>
       <c r="N9" t="n">
-        <v>0.4999</v>
+        <v>0.441</v>
       </c>
       <c r="O9" t="n">
-        <v>0.6076</v>
+        <v>0.5525</v>
       </c>
       <c r="P9" t="n">
-        <v>0.923</v>
+        <v>0.918</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.1538</v>
+        <v>-1.1475</v>
       </c>
       <c r="R9" t="n">
-        <v>2.0768</v>
+        <v>2.0655</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.8702</v>
+        <v>-0.8032</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.1213</v>
+        <v>-0.1786</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.7489</v>
+        <v>-0.6246</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.1462</v>
+        <v>-0.1509</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.1462</v>
+        <v>-0.1509</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1234,67 +1234,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.33</v>
+        <v>0.3718</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.7346</v>
+        <v>-0.6882</v>
       </c>
       <c r="F10" t="n">
-        <v>1.0646</v>
+        <v>1.06</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.0265</v>
+        <v>-0.0396</v>
       </c>
       <c r="H10" t="n">
-        <v>0.8433</v>
+        <v>0.8260999999999999</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.8698</v>
+        <v>-0.8656</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.7995</v>
+        <v>-0.7272999999999999</v>
       </c>
       <c r="K10" t="n">
-        <v>0.0049</v>
+        <v>0.0441</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.8044</v>
+        <v>-0.7714</v>
       </c>
       <c r="M10" t="n">
-        <v>0.7729</v>
+        <v>0.6878</v>
       </c>
       <c r="N10" t="n">
-        <v>0.8384</v>
+        <v>0.782</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.0654</v>
+        <v>-0.09429999999999999</v>
       </c>
       <c r="P10" t="n">
-        <v>1.1538</v>
+        <v>1.1475</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.1538</v>
+        <v>1.1475</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.0433</v>
+        <v>-0.9754</v>
       </c>
       <c r="T10" t="n">
-        <v>0.0649</v>
+        <v>0.0391</v>
       </c>
       <c r="U10" t="n">
-        <v>-1.1082</v>
+        <v>-1.0145</v>
       </c>
       <c r="V10" t="n">
-        <v>0.2461</v>
+        <v>0.2393</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0.2461</v>
+        <v>0.2393</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1320,64 +1320,64 @@
         <v>-1.5282</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.4066</v>
+        <v>-2.3782</v>
       </c>
       <c r="F11" t="n">
-        <v>0.8784</v>
+        <v>0.85</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.8249</v>
+        <v>-0.8673999999999999</v>
       </c>
       <c r="H11" t="n">
-        <v>0.3814</v>
+        <v>0.3216</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.2064</v>
+        <v>-1.189</v>
       </c>
       <c r="J11" t="n">
-        <v>-2.0978</v>
+        <v>-1.9961</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.4521</v>
+        <v>-0.4163</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.6457</v>
+        <v>-1.5798</v>
       </c>
       <c r="M11" t="n">
-        <v>1.2728</v>
+        <v>1.1287</v>
       </c>
       <c r="N11" t="n">
-        <v>0.8335</v>
+        <v>0.7379</v>
       </c>
       <c r="O11" t="n">
-        <v>0.4394</v>
+        <v>0.3908</v>
       </c>
       <c r="P11" t="n">
-        <v>1.846</v>
+        <v>1.836</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.846</v>
+        <v>1.836</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.4723</v>
+        <v>-1.4148</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.3088</v>
+        <v>-0.3821</v>
       </c>
       <c r="U11" t="n">
-        <v>-1.1635</v>
+        <v>-1.0327</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.077</v>
+        <v>-1.082</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.077</v>
+        <v>-1.082</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1400,67 +1400,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.899</v>
+        <v>-1.7596</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.3262</v>
+        <v>-3.1604</v>
       </c>
       <c r="F12" t="n">
-        <v>1.4272</v>
+        <v>1.4008</v>
       </c>
       <c r="G12" t="n">
-        <v>-1.7953</v>
+        <v>-1.7407</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.1391</v>
+        <v>-1.0537</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.6562</v>
+        <v>-0.6871</v>
       </c>
       <c r="J12" t="n">
-        <v>-2.6662</v>
+        <v>-2.4518</v>
       </c>
       <c r="K12" t="n">
-        <v>-1.9726</v>
+        <v>-1.7916</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.6936</v>
+        <v>-0.6602</v>
       </c>
       <c r="M12" t="n">
-        <v>0.8709</v>
+        <v>0.7111</v>
       </c>
       <c r="N12" t="n">
-        <v>0.8335</v>
+        <v>0.7379</v>
       </c>
       <c r="O12" t="n">
-        <v>0.0374</v>
+        <v>-0.0268</v>
       </c>
       <c r="P12" t="n">
-        <v>0.4615</v>
+        <v>0.459</v>
       </c>
       <c r="Q12" t="n">
-        <v>-2.3075</v>
+        <v>-2.295</v>
       </c>
       <c r="R12" t="n">
-        <v>2.7691</v>
+        <v>2.7539</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.7884</v>
+        <v>-1.7108</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.0143</v>
+        <v>-0.09909999999999999</v>
       </c>
       <c r="U12" t="n">
-        <v>-1.7741</v>
+        <v>-1.6117</v>
       </c>
       <c r="V12" t="n">
-        <v>1.2232</v>
+        <v>1.2329</v>
       </c>
       <c r="W12" t="n">
-        <v>1.6618</v>
+        <v>1.6855</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.4386</v>
+        <v>-0.4526</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1483,67 +1483,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>21.4178</v>
+        <v>21.6027</v>
       </c>
       <c r="E13" t="n">
-        <v>3.107</v>
+        <v>3.5941</v>
       </c>
       <c r="F13" t="n">
-        <v>18.3109</v>
+        <v>18.0087</v>
       </c>
       <c r="G13" t="n">
-        <v>9.452500000000002</v>
+        <v>9.437099999999999</v>
       </c>
       <c r="H13" t="n">
-        <v>1.7169</v>
+        <v>1.9254</v>
       </c>
       <c r="I13" t="n">
-        <v>7.7355</v>
+        <v>7.511699999999998</v>
       </c>
       <c r="J13" t="n">
-        <v>0.7339000000000007</v>
+        <v>2.2378</v>
       </c>
       <c r="K13" t="n">
-        <v>-4.9451</v>
+        <v>-3.9252</v>
       </c>
       <c r="L13" t="n">
-        <v>5.678900000000002</v>
+        <v>6.163</v>
       </c>
       <c r="M13" t="n">
-        <v>8.718500000000001</v>
+        <v>7.199300000000001</v>
       </c>
       <c r="N13" t="n">
-        <v>6.662</v>
+        <v>5.8505</v>
       </c>
       <c r="O13" t="n">
-        <v>2.0567</v>
+        <v>1.3487</v>
       </c>
       <c r="P13" t="n">
-        <v>12.6915</v>
+        <v>12.6225</v>
       </c>
       <c r="Q13" t="n">
-        <v>-8.076499999999999</v>
+        <v>-8.032499999999999</v>
       </c>
       <c r="R13" t="n">
-        <v>20.7679</v>
+        <v>20.65479999999999</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.8031</v>
+        <v>-1.5387</v>
       </c>
       <c r="T13" t="n">
-        <v>6.5874</v>
+        <v>5.4766</v>
       </c>
       <c r="U13" t="n">
-        <v>-8.3904</v>
+        <v>-7.015300000000001</v>
       </c>
       <c r="V13" t="n">
-        <v>1.077</v>
+        <v>1.082</v>
       </c>
       <c r="W13" t="n">
-        <v>3.8621</v>
+        <v>3.912100000000001</v>
       </c>
       <c r="X13" t="n">
-        <v>-2.7851</v>
+        <v>-2.83</v>
       </c>
       <c r="Y13" t="inlineStr"/>
     </row>
@@ -1562,64 +1562,64 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.1739</v>
+        <v>2.0952</v>
       </c>
       <c r="E14" t="n">
-        <v>1.6687</v>
+        <v>1.651</v>
       </c>
       <c r="F14" t="n">
-        <v>0.5052</v>
+        <v>0.4442</v>
       </c>
       <c r="G14" t="n">
-        <v>2.2002</v>
+        <v>2.1357</v>
       </c>
       <c r="H14" t="n">
-        <v>3.4926</v>
+        <v>3.4325</v>
       </c>
       <c r="I14" t="n">
-        <v>-1.2924</v>
+        <v>-1.2968</v>
       </c>
       <c r="J14" t="n">
-        <v>2.2718</v>
+        <v>2.4009</v>
       </c>
       <c r="K14" t="n">
-        <v>2.6621</v>
+        <v>2.721</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.3903</v>
+        <v>-0.3201</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.07149999999999999</v>
+        <v>-0.2651</v>
       </c>
       <c r="N14" t="n">
-        <v>0.8305</v>
+        <v>0.7115</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.9021</v>
+        <v>-0.9766</v>
       </c>
       <c r="P14" t="n">
-        <v>-1.3845</v>
+        <v>-1.377</v>
       </c>
       <c r="Q14" t="n">
-        <v>-2.5383</v>
+        <v>-2.5244</v>
       </c>
       <c r="R14" t="n">
-        <v>1.1538</v>
+        <v>1.1475</v>
       </c>
       <c r="S14" t="n">
-        <v>0.8197</v>
+        <v>0.7954</v>
       </c>
       <c r="T14" t="n">
-        <v>1.3967</v>
+        <v>1.2335</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.577</v>
+        <v>-0.4381</v>
       </c>
       <c r="V14" t="n">
-        <v>0.5385</v>
+        <v>0.541</v>
       </c>
       <c r="W14" t="n">
-        <v>0.5385</v>
+        <v>0.541</v>
       </c>
       <c r="X14" t="n">
         <v>0</v>
@@ -1645,67 +1645,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.2332</v>
+        <v>0.2091</v>
       </c>
       <c r="E15" t="n">
-        <v>-1.4442</v>
+        <v>-1.4182</v>
       </c>
       <c r="F15" t="n">
-        <v>1.6774</v>
+        <v>1.6272</v>
       </c>
       <c r="G15" t="n">
-        <v>0.6093</v>
+        <v>0.6155</v>
       </c>
       <c r="H15" t="n">
-        <v>1.6885</v>
+        <v>1.6698</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.0792</v>
+        <v>-1.0543</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.2943</v>
+        <v>-0.1428</v>
       </c>
       <c r="K15" t="n">
-        <v>0.6868</v>
+        <v>0.7702</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.9811</v>
+        <v>-0.9129</v>
       </c>
       <c r="M15" t="n">
-        <v>0.9036</v>
+        <v>0.7582</v>
       </c>
       <c r="N15" t="n">
-        <v>1.0017</v>
+        <v>0.8996</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.09810000000000001</v>
+        <v>-0.1414</v>
       </c>
       <c r="P15" t="n">
-        <v>-1.6153</v>
+        <v>-1.6065</v>
       </c>
       <c r="Q15" t="n">
-        <v>-2.5383</v>
+        <v>-2.5244</v>
       </c>
       <c r="R15" t="n">
-        <v>0.923</v>
+        <v>0.918</v>
       </c>
       <c r="S15" t="n">
-        <v>0.9146</v>
+        <v>0.8828</v>
       </c>
       <c r="T15" t="n">
-        <v>0.8499</v>
+        <v>0.708</v>
       </c>
       <c r="U15" t="n">
-        <v>0.0648</v>
+        <v>0.1747</v>
       </c>
       <c r="V15" t="n">
-        <v>0.3245</v>
+        <v>0.3173</v>
       </c>
       <c r="W15" t="n">
-        <v>0.5385</v>
+        <v>0.541</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.214</v>
+        <v>-0.2237</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
@@ -1728,40 +1728,40 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.3971</v>
+        <v>-0.4451</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.3042</v>
+        <v>-0.3357</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.0929</v>
+        <v>-0.1095</v>
       </c>
       <c r="G16" t="n">
-        <v>0.0332</v>
+        <v>-0.02</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.1393</v>
+        <v>-0.1717</v>
       </c>
       <c r="I16" t="n">
-        <v>0.1725</v>
+        <v>0.1516</v>
       </c>
       <c r="J16" t="n">
-        <v>0.0708</v>
+        <v>0.0712</v>
       </c>
       <c r="K16" t="n">
-        <v>0.0338</v>
+        <v>0.0341</v>
       </c>
       <c r="L16" t="n">
-        <v>0.0369</v>
+        <v>0.0371</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.0376</v>
+        <v>-0.0912</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.1732</v>
+        <v>-0.2058</v>
       </c>
       <c r="O16" t="n">
-        <v>0.1355</v>
+        <v>0.1146</v>
       </c>
       <c r="P16" t="n">
         <v>0</v>
@@ -1773,13 +1773,13 @@
         <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.4303</v>
+        <v>-0.4251</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.3749</v>
+        <v>-0.4068</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.0553</v>
+        <v>-0.0183</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1811,67 +1811,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.6427</v>
+        <v>-0.5452</v>
       </c>
       <c r="E17" t="n">
-        <v>0.5355</v>
+        <v>0.6831</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.1782</v>
+        <v>-1.2284</v>
       </c>
       <c r="G17" t="n">
-        <v>-3.8848</v>
+        <v>-3.762</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.8001</v>
+        <v>-1.7274</v>
       </c>
       <c r="I17" t="n">
-        <v>-2.0846</v>
+        <v>-2.0345</v>
       </c>
       <c r="J17" t="n">
-        <v>-2.9719</v>
+        <v>-2.6884</v>
       </c>
       <c r="K17" t="n">
-        <v>-2.2941</v>
+        <v>-2.1155</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.6777</v>
+        <v>-0.5728</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.9129</v>
+        <v>-1.0736</v>
       </c>
       <c r="N17" t="n">
-        <v>0.494</v>
+        <v>0.3881</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.4069</v>
+        <v>-1.4617</v>
       </c>
       <c r="P17" t="n">
-        <v>0.923</v>
+        <v>0.918</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0.923</v>
+        <v>0.918</v>
       </c>
       <c r="S17" t="n">
-        <v>0.3113</v>
+        <v>0.2856</v>
       </c>
       <c r="T17" t="n">
-        <v>1.3534</v>
+        <v>1.2075</v>
       </c>
       <c r="U17" t="n">
-        <v>-1.0421</v>
+        <v>-0.9219000000000001</v>
       </c>
       <c r="V17" t="n">
-        <v>2.0078</v>
+        <v>2.0132</v>
       </c>
       <c r="W17" t="n">
-        <v>2.154</v>
+        <v>2.164</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.1462</v>
+        <v>-0.1509</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
@@ -1894,67 +1894,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.3508</v>
+        <v>-1.4337</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.4556</v>
+        <v>-0.49</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.8951</v>
+        <v>-0.9436</v>
       </c>
       <c r="G18" t="n">
-        <v>0.6395999999999999</v>
+        <v>0.5455</v>
       </c>
       <c r="H18" t="n">
-        <v>0.8364</v>
+        <v>0.7644</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.1968</v>
+        <v>-0.2189</v>
       </c>
       <c r="J18" t="n">
-        <v>0.0418</v>
+        <v>0.08110000000000001</v>
       </c>
       <c r="K18" t="n">
-        <v>0.8462</v>
+        <v>0.8525</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.8044</v>
+        <v>-0.7714</v>
       </c>
       <c r="M18" t="n">
-        <v>0.5978</v>
+        <v>0.4644</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.0098</v>
+        <v>-0.0881</v>
       </c>
       <c r="O18" t="n">
-        <v>0.6076</v>
+        <v>0.5525</v>
       </c>
       <c r="P18" t="n">
-        <v>0.2308</v>
+        <v>0.2295</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0.2308</v>
+        <v>0.2295</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.1442</v>
+        <v>-1.1266</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.4975</v>
+        <v>-0.5711000000000001</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.6467000000000001</v>
+        <v>-0.5555</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.077</v>
+        <v>-1.082</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.077</v>
+        <v>-1.082</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
@@ -1977,67 +1977,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.5786</v>
+        <v>-1.6255</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.5415</v>
+        <v>-1.5368</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.0371</v>
+        <v>-0.0886</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.6904</v>
+        <v>-1.7109</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.3908</v>
+        <v>-1.4246</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.2996</v>
+        <v>-0.2863</v>
       </c>
       <c r="J19" t="n">
-        <v>-1.6803</v>
+        <v>-1.5048</v>
       </c>
       <c r="K19" t="n">
-        <v>-1.8808</v>
+        <v>-1.7774</v>
       </c>
       <c r="L19" t="n">
-        <v>0.2005</v>
+        <v>0.2727</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.01</v>
+        <v>-0.2062</v>
       </c>
       <c r="N19" t="n">
-        <v>0.4901</v>
+        <v>0.3528</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.5001</v>
+        <v>-0.5590000000000001</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.923</v>
+        <v>-0.918</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.6153</v>
+        <v>-1.6065</v>
       </c>
       <c r="R19" t="n">
-        <v>0.6923</v>
+        <v>0.6885</v>
       </c>
       <c r="S19" t="n">
-        <v>0.8101</v>
+        <v>0.7745</v>
       </c>
       <c r="T19" t="n">
-        <v>1.4617</v>
+        <v>1.2727</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.6516</v>
+        <v>-0.4981</v>
       </c>
       <c r="V19" t="n">
-        <v>0.2247</v>
+        <v>0.2289</v>
       </c>
       <c r="W19" t="n">
-        <v>0.2924</v>
+        <v>0.3017</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.0678</v>
+        <v>-0.0728</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
@@ -2060,58 +2060,58 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.6941</v>
+        <v>-2.6567</v>
       </c>
       <c r="E20" t="n">
-        <v>-3.9574</v>
+        <v>-3.9168</v>
       </c>
       <c r="F20" t="n">
-        <v>1.2633</v>
+        <v>1.2601</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.9935</v>
+        <v>-0.9837</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.2877</v>
+        <v>-0.2899</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.7058</v>
+        <v>-0.6939</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.6319</v>
+        <v>-1.5657</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.7906</v>
+        <v>-0.7573</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.8413</v>
+        <v>-0.8084</v>
       </c>
       <c r="M20" t="n">
-        <v>0.6384</v>
+        <v>0.582</v>
       </c>
       <c r="N20" t="n">
-        <v>0.5028</v>
+        <v>0.4674</v>
       </c>
       <c r="O20" t="n">
-        <v>0.1355</v>
+        <v>0.1146</v>
       </c>
       <c r="P20" t="n">
-        <v>-1.846</v>
+        <v>-1.836</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.3075</v>
+        <v>-2.295</v>
       </c>
       <c r="R20" t="n">
-        <v>0.4615</v>
+        <v>0.459</v>
       </c>
       <c r="S20" t="n">
-        <v>0.1454</v>
+        <v>0.163</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.018</v>
+        <v>-0.0561</v>
       </c>
       <c r="U20" t="n">
-        <v>0.1634</v>
+        <v>0.2191</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2143,67 +2143,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.3054</v>
+        <v>-3.3401</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.8991</v>
+        <v>-2.9036</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.4063</v>
+        <v>-0.4365</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.5855</v>
+        <v>-2.5702</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.5953000000000001</v>
+        <v>-0.6232</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.9902</v>
+        <v>-1.9469</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.7747</v>
+        <v>-1.6732</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.7567</v>
+        <v>-0.7232</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.018</v>
+        <v>-0.95</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.8108</v>
+        <v>-0.897</v>
       </c>
       <c r="N21" t="n">
-        <v>0.1614</v>
+        <v>0.1</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.9722</v>
+        <v>-0.9969</v>
       </c>
       <c r="P21" t="n">
-        <v>-1.3845</v>
+        <v>-1.377</v>
       </c>
       <c r="Q21" t="n">
-        <v>-2.5383</v>
+        <v>-2.5244</v>
       </c>
       <c r="R21" t="n">
-        <v>1.1538</v>
+        <v>1.1475</v>
       </c>
       <c r="S21" t="n">
-        <v>0.4399</v>
+        <v>0.3781</v>
       </c>
       <c r="T21" t="n">
-        <v>1.1215</v>
+        <v>0.9923</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.6815</v>
+        <v>-0.6142</v>
       </c>
       <c r="V21" t="n">
-        <v>0.2247</v>
+        <v>0.2289</v>
       </c>
       <c r="W21" t="n">
-        <v>0.2924</v>
+        <v>0.3017</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.0678</v>
+        <v>-0.0728</v>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
@@ -2226,67 +2226,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.9616</v>
+        <v>-3.9791</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.3747</v>
+        <v>-2.3116</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.5869</v>
+        <v>-1.6676</v>
       </c>
       <c r="G22" t="n">
-        <v>1.596</v>
+        <v>1.5915</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.1722</v>
+        <v>-0.1969</v>
       </c>
       <c r="I22" t="n">
-        <v>1.7682</v>
+        <v>1.7885</v>
       </c>
       <c r="J22" t="n">
-        <v>1.8417</v>
+        <v>2.0713</v>
       </c>
       <c r="K22" t="n">
-        <v>-1.1651</v>
+        <v>-1.0172</v>
       </c>
       <c r="L22" t="n">
-        <v>3.0068</v>
+        <v>3.0885</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.2457</v>
+        <v>-0.4797</v>
       </c>
       <c r="N22" t="n">
-        <v>0.9929</v>
+        <v>0.8203</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.2386</v>
+        <v>-1.3</v>
       </c>
       <c r="P22" t="n">
-        <v>-4.1536</v>
+        <v>-4.1309</v>
       </c>
       <c r="Q22" t="n">
-        <v>-5.0766</v>
+        <v>-5.0489</v>
       </c>
       <c r="R22" t="n">
-        <v>0.923</v>
+        <v>0.918</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.0132</v>
+        <v>-0.0456</v>
       </c>
       <c r="T22" t="n">
-        <v>1.2525</v>
+        <v>1.0562</v>
       </c>
       <c r="U22" t="n">
-        <v>-1.2657</v>
+        <v>-1.1018</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.3908</v>
+        <v>-1.3941</v>
       </c>
       <c r="W22" t="n">
-        <v>-0.3923</v>
+        <v>-0.3901</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.9985000000000001</v>
+        <v>-1.004</v>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
@@ -2309,67 +2309,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.0276</v>
+        <v>-3.9848</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.5382</v>
+        <v>-3.4602</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.4894</v>
+        <v>-0.5245</v>
       </c>
       <c r="G23" t="n">
-        <v>-4.4691</v>
+        <v>-4.3418</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.8956</v>
+        <v>-1.9097</v>
       </c>
       <c r="I23" t="n">
-        <v>-2.5735</v>
+        <v>-2.4322</v>
       </c>
       <c r="J23" t="n">
-        <v>-3.0504</v>
+        <v>-2.7743</v>
       </c>
       <c r="K23" t="n">
-        <v>-2.3886</v>
+        <v>-2.2889</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.6619</v>
+        <v>-0.4854</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.4186</v>
+        <v>-1.5675</v>
       </c>
       <c r="N23" t="n">
-        <v>0.493</v>
+        <v>0.3793</v>
       </c>
       <c r="O23" t="n">
-        <v>-1.9117</v>
+        <v>-1.9468</v>
       </c>
       <c r="P23" t="n">
-        <v>-1.1538</v>
+        <v>-1.1475</v>
       </c>
       <c r="Q23" t="n">
-        <v>-2.7691</v>
+        <v>-2.7539</v>
       </c>
       <c r="R23" t="n">
-        <v>1.6153</v>
+        <v>1.6065</v>
       </c>
       <c r="S23" t="n">
-        <v>1.5168</v>
+        <v>1.4265</v>
       </c>
       <c r="T23" t="n">
-        <v>2.2813</v>
+        <v>2.0681</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.7645</v>
+        <v>-0.6415</v>
       </c>
       <c r="V23" t="n">
-        <v>0.0785</v>
+        <v>0.078</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>0.0785</v>
+        <v>0.078</v>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
@@ -2392,67 +2392,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.4009</v>
+        <v>-4.4103</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.2156</v>
+        <v>-3.1897</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.1853</v>
+        <v>-1.2206</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.9076</v>
+        <v>-0.9367</v>
       </c>
       <c r="H24" t="n">
-        <v>-1.4536</v>
+        <v>-1.4487</v>
       </c>
       <c r="I24" t="n">
-        <v>0.5459000000000001</v>
+        <v>0.512</v>
       </c>
       <c r="J24" t="n">
-        <v>-1.5411</v>
+        <v>-1.4746</v>
       </c>
       <c r="K24" t="n">
-        <v>-1.615</v>
+        <v>-1.5487</v>
       </c>
       <c r="L24" t="n">
-        <v>0.0738</v>
+        <v>0.0741</v>
       </c>
       <c r="M24" t="n">
-        <v>0.6335</v>
+        <v>0.5379</v>
       </c>
       <c r="N24" t="n">
-        <v>0.1614</v>
+        <v>0.1</v>
       </c>
       <c r="O24" t="n">
-        <v>0.4721</v>
+        <v>0.4379</v>
       </c>
       <c r="P24" t="n">
-        <v>-1.3845</v>
+        <v>-1.377</v>
       </c>
       <c r="Q24" t="n">
-        <v>-1.3845</v>
+        <v>-1.377</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.101</v>
+        <v>-0.0835</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.4362</v>
+        <v>-0.489</v>
       </c>
       <c r="U24" t="n">
-        <v>0.3352</v>
+        <v>0.4055</v>
       </c>
       <c r="V24" t="n">
-        <v>-2.0078</v>
+        <v>-2.0132</v>
       </c>
       <c r="W24" t="n">
-        <v>0.1462</v>
+        <v>0.1509</v>
       </c>
       <c r="X24" t="n">
-        <v>-2.154</v>
+        <v>-2.164</v>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
@@ -2475,67 +2475,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-19.9517</v>
+        <v>-20.1162</v>
       </c>
       <c r="E25" t="n">
-        <v>-17.5263</v>
+        <v>-17.2285</v>
       </c>
       <c r="F25" t="n">
-        <v>-2.4253</v>
+        <v>-2.887799999999999</v>
       </c>
       <c r="G25" t="n">
-        <v>-9.452600000000002</v>
+        <v>-9.437099999999999</v>
       </c>
       <c r="H25" t="n">
-        <v>-1.7171</v>
+        <v>-1.9254</v>
       </c>
       <c r="I25" t="n">
-        <v>-7.735499999999998</v>
+        <v>-7.511699999999999</v>
       </c>
       <c r="J25" t="n">
-        <v>-8.718500000000001</v>
+        <v>-7.1993</v>
       </c>
       <c r="K25" t="n">
-        <v>-6.662000000000001</v>
+        <v>-5.8504</v>
       </c>
       <c r="L25" t="n">
-        <v>-2.056700000000001</v>
+        <v>-1.3486</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.7338000000000002</v>
+        <v>-2.2378</v>
       </c>
       <c r="N25" t="n">
-        <v>4.944800000000001</v>
+        <v>3.9251</v>
       </c>
       <c r="O25" t="n">
-        <v>-5.678999999999999</v>
+        <v>-6.1628</v>
       </c>
       <c r="P25" t="n">
-        <v>-12.6914</v>
+        <v>-12.6224</v>
       </c>
       <c r="Q25" t="n">
-        <v>-20.7679</v>
+        <v>-20.6545</v>
       </c>
       <c r="R25" t="n">
-        <v>8.076499999999999</v>
+        <v>8.032500000000001</v>
       </c>
       <c r="S25" t="n">
-        <v>3.2691</v>
+        <v>3.0251</v>
       </c>
       <c r="T25" t="n">
-        <v>8.3904</v>
+        <v>7.015299999999999</v>
       </c>
       <c r="U25" t="n">
-        <v>-5.121</v>
+        <v>-3.9901</v>
       </c>
       <c r="V25" t="n">
-        <v>-1.0769</v>
+        <v>-1.082</v>
       </c>
       <c r="W25" t="n">
-        <v>3.5697</v>
+        <v>3.610200000000001</v>
       </c>
       <c r="X25" t="n">
-        <v>-4.6468</v>
+        <v>-4.692200000000001</v>
       </c>
       <c r="Y25" t="inlineStr"/>
     </row>

--- a/informes_data/ACB/2025-26/playoffs/individual/NP_play_by_play_105353_W2.xlsx
+++ b/informes_data/ACB/2025-26/playoffs/individual/NP_play_by_play_105353_W2.xlsx
@@ -570,64 +570,64 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>10.4671</v>
+        <v>10.3213</v>
       </c>
       <c r="E2" t="n">
-        <v>9.0585</v>
+        <v>8.7193</v>
       </c>
       <c r="F2" t="n">
-        <v>1.4086</v>
+        <v>1.602</v>
       </c>
       <c r="G2" t="n">
-        <v>7.4909</v>
+        <v>7.3612</v>
       </c>
       <c r="H2" t="n">
-        <v>-1.8021</v>
+        <v>-1.8285</v>
       </c>
       <c r="I2" t="n">
-        <v>9.292999999999999</v>
+        <v>9.1897</v>
       </c>
       <c r="J2" t="n">
-        <v>7.7943</v>
+        <v>7.5882</v>
       </c>
       <c r="K2" t="n">
-        <v>-2.0374</v>
+        <v>-2.1067</v>
       </c>
       <c r="L2" t="n">
-        <v>9.8317</v>
+        <v>9.694900000000001</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.3035</v>
+        <v>-0.227</v>
       </c>
       <c r="N2" t="n">
-        <v>0.2352</v>
+        <v>0.2782</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.5387</v>
+        <v>-0.5051</v>
       </c>
       <c r="P2" t="n">
-        <v>1.1475</v>
+        <v>1.1699</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.1475</v>
+        <v>-1.1699</v>
       </c>
       <c r="R2" t="n">
-        <v>2.295</v>
+        <v>2.3397</v>
       </c>
       <c r="S2" t="n">
-        <v>0.5959</v>
+        <v>0.5918</v>
       </c>
       <c r="T2" t="n">
-        <v>1.1788</v>
+        <v>1.1026</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.5829</v>
+        <v>-0.5108</v>
       </c>
       <c r="V2" t="n">
-        <v>1.2329</v>
+        <v>1.1984</v>
       </c>
       <c r="W2" t="n">
-        <v>1.2329</v>
+        <v>1.1984</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
@@ -653,64 +653,64 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.9023</v>
+        <v>3.8932</v>
       </c>
       <c r="E3" t="n">
-        <v>0.8885999999999999</v>
+        <v>0.6981000000000001</v>
       </c>
       <c r="F3" t="n">
-        <v>3.0137</v>
+        <v>3.1951</v>
       </c>
       <c r="G3" t="n">
-        <v>1.1395</v>
+        <v>1.1147</v>
       </c>
       <c r="H3" t="n">
-        <v>1.3887</v>
+        <v>1.3646</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.2493</v>
+        <v>-0.2499</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1521</v>
+        <v>0.073</v>
       </c>
       <c r="K3" t="n">
-        <v>0.6508</v>
+        <v>0.5928</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.4987</v>
+        <v>-0.5197000000000001</v>
       </c>
       <c r="M3" t="n">
-        <v>0.9874000000000001</v>
+        <v>1.0416</v>
       </c>
       <c r="N3" t="n">
-        <v>0.7379</v>
+        <v>0.7718</v>
       </c>
       <c r="O3" t="n">
-        <v>0.2494</v>
+        <v>0.2699</v>
       </c>
       <c r="P3" t="n">
-        <v>1.6065</v>
+        <v>1.6378</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.1475</v>
+        <v>-1.1699</v>
       </c>
       <c r="R3" t="n">
-        <v>2.7539</v>
+        <v>2.8077</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0743</v>
+        <v>0.0766</v>
       </c>
       <c r="T3" t="n">
-        <v>0.8018999999999999</v>
+        <v>0.7308</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.7276</v>
+        <v>-0.6542</v>
       </c>
       <c r="V3" t="n">
-        <v>1.082</v>
+        <v>1.0641</v>
       </c>
       <c r="W3" t="n">
-        <v>1.082</v>
+        <v>1.0641</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
@@ -736,67 +736,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.3131</v>
+        <v>3.3655</v>
       </c>
       <c r="E4" t="n">
-        <v>1.7276</v>
+        <v>1.6354</v>
       </c>
       <c r="F4" t="n">
-        <v>1.5855</v>
+        <v>1.7301</v>
       </c>
       <c r="G4" t="n">
-        <v>1.242</v>
+        <v>1.2213</v>
       </c>
       <c r="H4" t="n">
-        <v>0.6491</v>
+        <v>0.6157</v>
       </c>
       <c r="I4" t="n">
-        <v>0.593</v>
+        <v>0.6056</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0194</v>
+        <v>-0.0383</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.277</v>
+        <v>-0.3311</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2964</v>
+        <v>0.2928</v>
       </c>
       <c r="M4" t="n">
-        <v>1.2226</v>
+        <v>1.2596</v>
       </c>
       <c r="N4" t="n">
-        <v>0.9261</v>
+        <v>0.9468</v>
       </c>
       <c r="O4" t="n">
-        <v>0.2966</v>
+        <v>0.3128</v>
       </c>
       <c r="P4" t="n">
-        <v>1.836</v>
+        <v>1.8718</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.836</v>
+        <v>1.8718</v>
       </c>
       <c r="S4" t="n">
-        <v>0.386</v>
+        <v>0.4067</v>
       </c>
       <c r="T4" t="n">
-        <v>1.7082</v>
+        <v>1.6737</v>
       </c>
       <c r="U4" t="n">
-        <v>-1.3222</v>
+        <v>-1.267</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.1509</v>
+        <v>-0.1343</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.1509</v>
+        <v>-0.1343</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
@@ -819,64 +819,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.0865</v>
+        <v>3.0441</v>
       </c>
       <c r="E5" t="n">
-        <v>2.3129</v>
+        <v>2.1919</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7736</v>
+        <v>0.8522</v>
       </c>
       <c r="G5" t="n">
-        <v>1.9564</v>
+        <v>1.9057</v>
       </c>
       <c r="H5" t="n">
-        <v>2.5829</v>
+        <v>2.5191</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.6264</v>
+        <v>-0.6135</v>
       </c>
       <c r="J5" t="n">
-        <v>2.1242</v>
+        <v>2.048</v>
       </c>
       <c r="K5" t="n">
-        <v>2.1242</v>
+        <v>2.048</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.1678</v>
+        <v>-0.1423</v>
       </c>
       <c r="N5" t="n">
-        <v>0.4586</v>
+        <v>0.4711</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.6264</v>
+        <v>-0.6135</v>
       </c>
       <c r="P5" t="n">
-        <v>1.1475</v>
+        <v>1.1699</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.1475</v>
+        <v>1.1699</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.1682</v>
+        <v>-0.1657</v>
       </c>
       <c r="T5" t="n">
-        <v>0.0378</v>
+        <v>0.009599999999999999</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.206</v>
+        <v>-0.1753</v>
       </c>
       <c r="V5" t="n">
-        <v>0.1509</v>
+        <v>0.1343</v>
       </c>
       <c r="W5" t="n">
-        <v>0.1509</v>
+        <v>0.1343</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -902,67 +902,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.8446</v>
+        <v>1.9137</v>
       </c>
       <c r="E6" t="n">
-        <v>0.2438</v>
+        <v>0.1285</v>
       </c>
       <c r="F6" t="n">
-        <v>1.6009</v>
+        <v>1.7852</v>
       </c>
       <c r="G6" t="n">
-        <v>1.0337</v>
+        <v>1.0608</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.3339</v>
+        <v>-0.3047</v>
       </c>
       <c r="I6" t="n">
-        <v>1.3676</v>
+        <v>1.3655</v>
       </c>
       <c r="J6" t="n">
-        <v>0.5988</v>
+        <v>0.5794</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.5868</v>
+        <v>-0.5919</v>
       </c>
       <c r="L6" t="n">
-        <v>1.1856</v>
+        <v>1.1713</v>
       </c>
       <c r="M6" t="n">
-        <v>0.4349</v>
+        <v>0.4814</v>
       </c>
       <c r="N6" t="n">
-        <v>0.2529</v>
+        <v>0.2872</v>
       </c>
       <c r="O6" t="n">
-        <v>0.182</v>
+        <v>0.1942</v>
       </c>
       <c r="P6" t="n">
-        <v>0.6885</v>
+        <v>0.7019</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.1475</v>
+        <v>-1.1699</v>
       </c>
       <c r="R6" t="n">
-        <v>1.836</v>
+        <v>1.8718</v>
       </c>
       <c r="S6" t="n">
-        <v>1.0536</v>
+        <v>1.0808</v>
       </c>
       <c r="T6" t="n">
-        <v>0.6415</v>
+        <v>0.5847</v>
       </c>
       <c r="U6" t="n">
-        <v>0.412</v>
+        <v>0.4961</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.9312</v>
+        <v>-0.9298</v>
       </c>
       <c r="W6" t="n">
-        <v>0.1509</v>
+        <v>0.1343</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.082</v>
+        <v>-1.0641</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -985,67 +985,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.7362</v>
+        <v>0.8037</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.969</v>
+        <v>-2.038</v>
       </c>
       <c r="F7" t="n">
-        <v>2.7052</v>
+        <v>2.8418</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.8404</v>
+        <v>-0.8397</v>
       </c>
       <c r="H7" t="n">
-        <v>0.2475</v>
+        <v>0.2369</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.088</v>
+        <v>-1.0766</v>
       </c>
       <c r="J7" t="n">
-        <v>-2.1278</v>
+        <v>-2.1512</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.6962</v>
+        <v>-0.7188</v>
       </c>
       <c r="L7" t="n">
-        <v>-1.4316</v>
+        <v>-1.4324</v>
       </c>
       <c r="M7" t="n">
-        <v>1.2874</v>
+        <v>1.3115</v>
       </c>
       <c r="N7" t="n">
-        <v>0.9437</v>
+        <v>0.9558</v>
       </c>
       <c r="O7" t="n">
-        <v>0.3437</v>
+        <v>0.3558</v>
       </c>
       <c r="P7" t="n">
-        <v>1.377</v>
+        <v>1.4038</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.377</v>
+        <v>1.4038</v>
       </c>
       <c r="S7" t="n">
-        <v>0.7406</v>
+        <v>0.7716</v>
       </c>
       <c r="T7" t="n">
-        <v>0.549</v>
+        <v>0.5109</v>
       </c>
       <c r="U7" t="n">
-        <v>0.1917</v>
+        <v>0.2607</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.541</v>
+        <v>-0.5321</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.3901</v>
+        <v>-0.3978</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.1509</v>
+        <v>-0.1343</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1068,58 +1068,58 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6319</v>
+        <v>0.6257</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.695</v>
+        <v>-0.8433</v>
       </c>
       <c r="F8" t="n">
-        <v>1.3269</v>
+        <v>1.469</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.5104</v>
+        <v>-0.519</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.6928</v>
+        <v>-1.7015</v>
       </c>
       <c r="I8" t="n">
-        <v>1.1824</v>
+        <v>1.1825</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.7276</v>
+        <v>-0.7914</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.29</v>
+        <v>-1.3381</v>
       </c>
       <c r="L8" t="n">
-        <v>0.5624</v>
+        <v>0.5466</v>
       </c>
       <c r="M8" t="n">
-        <v>0.2172</v>
+        <v>0.2724</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.4027</v>
+        <v>-0.3635</v>
       </c>
       <c r="O8" t="n">
-        <v>0.6199</v>
+        <v>0.6359</v>
       </c>
       <c r="P8" t="n">
-        <v>0.459</v>
+        <v>0.4679</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.1475</v>
+        <v>-1.1699</v>
       </c>
       <c r="R8" t="n">
-        <v>1.6065</v>
+        <v>1.6378</v>
       </c>
       <c r="S8" t="n">
-        <v>0.6833</v>
+        <v>0.6768</v>
       </c>
       <c r="T8" t="n">
-        <v>1.1801</v>
+        <v>1.118</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.4968</v>
+        <v>-0.4412</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1151,67 +1151,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.537</v>
+        <v>0.5917</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.7465</v>
+        <v>-1.8357</v>
       </c>
       <c r="F9" t="n">
-        <v>2.2835</v>
+        <v>2.4273</v>
       </c>
       <c r="G9" t="n">
-        <v>0.5731000000000001</v>
+        <v>0.5726</v>
       </c>
       <c r="H9" t="n">
-        <v>0.792</v>
+        <v>0.7835</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.2189</v>
+        <v>-0.2108</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.4204</v>
+        <v>-0.4498</v>
       </c>
       <c r="K9" t="n">
-        <v>0.351</v>
+        <v>0.3213</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.7714</v>
+        <v>-0.7711</v>
       </c>
       <c r="M9" t="n">
-        <v>0.9935</v>
+        <v>1.0224</v>
       </c>
       <c r="N9" t="n">
-        <v>0.441</v>
+        <v>0.4622</v>
       </c>
       <c r="O9" t="n">
-        <v>0.5525</v>
+        <v>0.5603</v>
       </c>
       <c r="P9" t="n">
-        <v>0.918</v>
+        <v>0.9359</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.1475</v>
+        <v>-1.1699</v>
       </c>
       <c r="R9" t="n">
-        <v>2.0655</v>
+        <v>2.1057</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.8032</v>
+        <v>-0.7825</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.1786</v>
+        <v>-0.216</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.6246</v>
+        <v>-0.5665</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.1509</v>
+        <v>-0.1343</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.1509</v>
+        <v>-0.1343</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1234,67 +1234,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.3718</v>
+        <v>0.435</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.6882</v>
+        <v>-0.7236</v>
       </c>
       <c r="F10" t="n">
-        <v>1.06</v>
+        <v>1.1586</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.0396</v>
+        <v>-0.0403</v>
       </c>
       <c r="H10" t="n">
-        <v>0.8260999999999999</v>
+        <v>0.8167</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.8656</v>
+        <v>-0.857</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.7272999999999999</v>
+        <v>-0.7486</v>
       </c>
       <c r="K10" t="n">
-        <v>0.0441</v>
+        <v>0.0224</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.7714</v>
+        <v>-0.7711</v>
       </c>
       <c r="M10" t="n">
-        <v>0.6878</v>
+        <v>0.7083</v>
       </c>
       <c r="N10" t="n">
-        <v>0.782</v>
+        <v>0.7942</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.09429999999999999</v>
+        <v>-0.0859</v>
       </c>
       <c r="P10" t="n">
-        <v>1.1475</v>
+        <v>1.1699</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.1475</v>
+        <v>1.1699</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.9754</v>
+        <v>-0.958</v>
       </c>
       <c r="T10" t="n">
-        <v>0.0391</v>
+        <v>0.025</v>
       </c>
       <c r="U10" t="n">
-        <v>-1.0145</v>
+        <v>-0.983</v>
       </c>
       <c r="V10" t="n">
-        <v>0.2393</v>
+        <v>0.2634</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0.2393</v>
+        <v>0.2634</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1317,67 +1317,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.5282</v>
+        <v>-1.4399</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.3782</v>
+        <v>-2.4379</v>
       </c>
       <c r="F11" t="n">
-        <v>0.85</v>
+        <v>0.998</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.8673999999999999</v>
+        <v>-0.8341</v>
       </c>
       <c r="H11" t="n">
-        <v>0.3216</v>
+        <v>0.346</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.189</v>
+        <v>-1.1801</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.9961</v>
+        <v>-2.0046</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.4163</v>
+        <v>-0.4258</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.5798</v>
+        <v>-1.5788</v>
       </c>
       <c r="M11" t="n">
-        <v>1.1287</v>
+        <v>1.1705</v>
       </c>
       <c r="N11" t="n">
-        <v>0.7379</v>
+        <v>0.7718</v>
       </c>
       <c r="O11" t="n">
-        <v>0.3908</v>
+        <v>0.3987</v>
       </c>
       <c r="P11" t="n">
-        <v>1.836</v>
+        <v>1.8718</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.836</v>
+        <v>1.8718</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.4148</v>
+        <v>-1.4135</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.3821</v>
+        <v>-0.4333</v>
       </c>
       <c r="U11" t="n">
-        <v>-1.0327</v>
+        <v>-0.9802</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.082</v>
+        <v>-1.0641</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.082</v>
+        <v>-1.0641</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1400,67 +1400,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.7596</v>
+        <v>-1.7848</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.1604</v>
+        <v>-3.3972</v>
       </c>
       <c r="F12" t="n">
-        <v>1.4008</v>
+        <v>1.6124</v>
       </c>
       <c r="G12" t="n">
-        <v>-1.7407</v>
+        <v>-1.7467</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.0537</v>
+        <v>-1.0751</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.6871</v>
+        <v>-0.6715</v>
       </c>
       <c r="J12" t="n">
-        <v>-2.4518</v>
+        <v>-2.5082</v>
       </c>
       <c r="K12" t="n">
-        <v>-1.7916</v>
+        <v>-1.8469</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.6602</v>
+        <v>-0.6613</v>
       </c>
       <c r="M12" t="n">
-        <v>0.7111</v>
+        <v>0.7615</v>
       </c>
       <c r="N12" t="n">
-        <v>0.7379</v>
+        <v>0.7718</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.0268</v>
+        <v>-0.0103</v>
       </c>
       <c r="P12" t="n">
-        <v>0.459</v>
+        <v>0.4679</v>
       </c>
       <c r="Q12" t="n">
-        <v>-2.295</v>
+        <v>-2.3397</v>
       </c>
       <c r="R12" t="n">
-        <v>2.7539</v>
+        <v>2.8077</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.7108</v>
+        <v>-1.7045</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.09909999999999999</v>
+        <v>-0.1506</v>
       </c>
       <c r="U12" t="n">
-        <v>-1.6117</v>
+        <v>-1.5539</v>
       </c>
       <c r="V12" t="n">
-        <v>1.2329</v>
+        <v>1.1984</v>
       </c>
       <c r="W12" t="n">
-        <v>1.6855</v>
+        <v>1.6013</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.4526</v>
+        <v>-0.4029</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1483,67 +1483,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>21.6027</v>
+        <v>21.76919999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>3.5941</v>
+        <v>2.097500000000001</v>
       </c>
       <c r="F13" t="n">
-        <v>18.0087</v>
+        <v>19.6717</v>
       </c>
       <c r="G13" t="n">
-        <v>9.437099999999999</v>
+        <v>9.256499999999997</v>
       </c>
       <c r="H13" t="n">
-        <v>1.9254</v>
+        <v>1.772699999999999</v>
       </c>
       <c r="I13" t="n">
-        <v>7.511699999999998</v>
+        <v>7.483900000000002</v>
       </c>
       <c r="J13" t="n">
-        <v>2.2378</v>
+        <v>1.5965</v>
       </c>
       <c r="K13" t="n">
-        <v>-3.9252</v>
+        <v>-4.3748</v>
       </c>
       <c r="L13" t="n">
-        <v>6.163</v>
+        <v>5.9712</v>
       </c>
       <c r="M13" t="n">
-        <v>7.199300000000001</v>
+        <v>7.6599</v>
       </c>
       <c r="N13" t="n">
-        <v>5.8505</v>
+        <v>6.147399999999999</v>
       </c>
       <c r="O13" t="n">
-        <v>1.3487</v>
+        <v>1.5128</v>
       </c>
       <c r="P13" t="n">
-        <v>12.6225</v>
+        <v>12.8685</v>
       </c>
       <c r="Q13" t="n">
-        <v>-8.032499999999999</v>
+        <v>-8.1892</v>
       </c>
       <c r="R13" t="n">
-        <v>20.65479999999999</v>
+        <v>21.0576</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.5387</v>
+        <v>-1.4199</v>
       </c>
       <c r="T13" t="n">
-        <v>5.4766</v>
+        <v>4.955400000000001</v>
       </c>
       <c r="U13" t="n">
-        <v>-7.015300000000001</v>
+        <v>-6.375300000000001</v>
       </c>
       <c r="V13" t="n">
-        <v>1.082</v>
+        <v>1.064</v>
       </c>
       <c r="W13" t="n">
-        <v>3.912100000000001</v>
+        <v>3.7346</v>
       </c>
       <c r="X13" t="n">
-        <v>-2.83</v>
+        <v>-2.6706</v>
       </c>
       <c r="Y13" t="inlineStr"/>
     </row>
@@ -1562,64 +1562,64 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.0952</v>
+        <v>2.0339</v>
       </c>
       <c r="E14" t="n">
-        <v>1.651</v>
+        <v>1.4199</v>
       </c>
       <c r="F14" t="n">
-        <v>0.4442</v>
+        <v>0.614</v>
       </c>
       <c r="G14" t="n">
-        <v>2.1357</v>
+        <v>2.1063</v>
       </c>
       <c r="H14" t="n">
-        <v>3.4325</v>
+        <v>3.3874</v>
       </c>
       <c r="I14" t="n">
-        <v>-1.2968</v>
+        <v>-1.2811</v>
       </c>
       <c r="J14" t="n">
-        <v>2.4009</v>
+        <v>2.2948</v>
       </c>
       <c r="K14" t="n">
-        <v>2.721</v>
+        <v>2.6291</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.3201</v>
+        <v>-0.3343</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.2651</v>
+        <v>-0.1885</v>
       </c>
       <c r="N14" t="n">
-        <v>0.7115</v>
+        <v>0.7583</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.9766</v>
+        <v>-0.9468</v>
       </c>
       <c r="P14" t="n">
-        <v>-1.377</v>
+        <v>-1.4038</v>
       </c>
       <c r="Q14" t="n">
-        <v>-2.5244</v>
+        <v>-2.5737</v>
       </c>
       <c r="R14" t="n">
-        <v>1.1475</v>
+        <v>1.1699</v>
       </c>
       <c r="S14" t="n">
-        <v>0.7954</v>
+        <v>0.7994</v>
       </c>
       <c r="T14" t="n">
-        <v>1.2335</v>
+        <v>1.1667</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.4381</v>
+        <v>-0.3674</v>
       </c>
       <c r="V14" t="n">
-        <v>0.541</v>
+        <v>0.5321</v>
       </c>
       <c r="W14" t="n">
-        <v>0.541</v>
+        <v>0.5321</v>
       </c>
       <c r="X14" t="n">
         <v>0</v>
@@ -1645,67 +1645,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.2091</v>
+        <v>0.183</v>
       </c>
       <c r="E15" t="n">
-        <v>-1.4182</v>
+        <v>-1.6109</v>
       </c>
       <c r="F15" t="n">
-        <v>1.6272</v>
+        <v>1.7939</v>
       </c>
       <c r="G15" t="n">
-        <v>0.6155</v>
+        <v>0.5935</v>
       </c>
       <c r="H15" t="n">
-        <v>1.6698</v>
+        <v>1.6423</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.0543</v>
+        <v>-1.0488</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.1428</v>
+        <v>-0.2109</v>
       </c>
       <c r="K15" t="n">
-        <v>0.7702</v>
+        <v>0.709</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.9129</v>
+        <v>-0.9199000000000001</v>
       </c>
       <c r="M15" t="n">
-        <v>0.7582</v>
+        <v>0.8045</v>
       </c>
       <c r="N15" t="n">
-        <v>0.8996</v>
+        <v>0.9333</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.1414</v>
+        <v>-0.1289</v>
       </c>
       <c r="P15" t="n">
-        <v>-1.6065</v>
+        <v>-1.6378</v>
       </c>
       <c r="Q15" t="n">
-        <v>-2.5244</v>
+        <v>-2.5737</v>
       </c>
       <c r="R15" t="n">
-        <v>0.918</v>
+        <v>0.9359</v>
       </c>
       <c r="S15" t="n">
-        <v>0.8828</v>
+        <v>0.8843</v>
       </c>
       <c r="T15" t="n">
-        <v>0.708</v>
+        <v>0.6417</v>
       </c>
       <c r="U15" t="n">
-        <v>0.1747</v>
+        <v>0.2426</v>
       </c>
       <c r="V15" t="n">
-        <v>0.3173</v>
+        <v>0.343</v>
       </c>
       <c r="W15" t="n">
-        <v>0.541</v>
+        <v>0.5321</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.2237</v>
+        <v>-0.1891</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
@@ -1728,40 +1728,40 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.4451</v>
+        <v>-0.4273</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.3357</v>
+        <v>-0.3648</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.1095</v>
+        <v>-0.0625</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.02</v>
+        <v>0.0044</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.1717</v>
+        <v>-0.1508</v>
       </c>
       <c r="I16" t="n">
-        <v>0.1516</v>
+        <v>0.1552</v>
       </c>
       <c r="J16" t="n">
-        <v>0.0712</v>
+        <v>0.0698</v>
       </c>
       <c r="K16" t="n">
-        <v>0.0341</v>
+        <v>0.0332</v>
       </c>
       <c r="L16" t="n">
-        <v>0.0371</v>
+        <v>0.0366</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.0912</v>
+        <v>-0.0654</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.2058</v>
+        <v>-0.184</v>
       </c>
       <c r="O16" t="n">
-        <v>0.1146</v>
+        <v>0.1186</v>
       </c>
       <c r="P16" t="n">
         <v>0</v>
@@ -1773,13 +1773,13 @@
         <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.4251</v>
+        <v>-0.4317</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.4068</v>
+        <v>-0.4346</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.0183</v>
+        <v>0.0029</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1811,67 +1811,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.5452</v>
+        <v>-0.5446</v>
       </c>
       <c r="E17" t="n">
-        <v>0.6831</v>
+        <v>0.523</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.2284</v>
+        <v>-1.0676</v>
       </c>
       <c r="G17" t="n">
-        <v>-3.762</v>
+        <v>-3.7515</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.7274</v>
+        <v>-1.7271</v>
       </c>
       <c r="I17" t="n">
-        <v>-2.0345</v>
+        <v>-2.0244</v>
       </c>
       <c r="J17" t="n">
-        <v>-2.6884</v>
+        <v>-2.7553</v>
       </c>
       <c r="K17" t="n">
-        <v>-2.1155</v>
+        <v>-2.1624</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.5728</v>
+        <v>-0.5929</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.0736</v>
+        <v>-0.9962</v>
       </c>
       <c r="N17" t="n">
-        <v>0.3881</v>
+        <v>0.4352</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.4617</v>
+        <v>-1.4314</v>
       </c>
       <c r="P17" t="n">
-        <v>0.918</v>
+        <v>0.9359</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0.918</v>
+        <v>0.9359</v>
       </c>
       <c r="S17" t="n">
-        <v>0.2856</v>
+        <v>0.2771</v>
       </c>
       <c r="T17" t="n">
-        <v>1.2075</v>
+        <v>1.15</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.9219000000000001</v>
+        <v>-0.8729</v>
       </c>
       <c r="V17" t="n">
-        <v>2.0132</v>
+        <v>1.9939</v>
       </c>
       <c r="W17" t="n">
-        <v>2.164</v>
+        <v>2.1282</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.1509</v>
+        <v>-0.1343</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
@@ -1894,67 +1894,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.4337</v>
+        <v>-1.3977</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.49</v>
+        <v>-0.5678</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.9436</v>
+        <v>-0.8299</v>
       </c>
       <c r="G18" t="n">
-        <v>0.5455</v>
+        <v>0.5744</v>
       </c>
       <c r="H18" t="n">
-        <v>0.7644</v>
+        <v>0.7852</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.2189</v>
+        <v>-0.2108</v>
       </c>
       <c r="J18" t="n">
-        <v>0.08110000000000001</v>
+        <v>0.059</v>
       </c>
       <c r="K18" t="n">
-        <v>0.8525</v>
+        <v>0.8300999999999999</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.7714</v>
+        <v>-0.7711</v>
       </c>
       <c r="M18" t="n">
-        <v>0.4644</v>
+        <v>0.5154</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.0881</v>
+        <v>-0.0449</v>
       </c>
       <c r="O18" t="n">
-        <v>0.5525</v>
+        <v>0.5603</v>
       </c>
       <c r="P18" t="n">
-        <v>0.2295</v>
+        <v>0.234</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0.2295</v>
+        <v>0.234</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.1266</v>
+        <v>-1.142</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.5711000000000001</v>
+        <v>-0.6269</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.5555</v>
+        <v>-0.5151</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.082</v>
+        <v>-1.0641</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.082</v>
+        <v>-1.0641</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
@@ -1977,67 +1977,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.6255</v>
+        <v>-1.6119</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.5368</v>
+        <v>-1.7183</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.0886</v>
+        <v>0.1064</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.7109</v>
+        <v>-1.6614</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.4246</v>
+        <v>-1.3749</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.2863</v>
+        <v>-0.2865</v>
       </c>
       <c r="J19" t="n">
-        <v>-1.5048</v>
+        <v>-1.5408</v>
       </c>
       <c r="K19" t="n">
-        <v>-1.7774</v>
+        <v>-1.7922</v>
       </c>
       <c r="L19" t="n">
-        <v>0.2727</v>
+        <v>0.2514</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.2062</v>
+        <v>-0.1205</v>
       </c>
       <c r="N19" t="n">
-        <v>0.3528</v>
+        <v>0.4173</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.5590000000000001</v>
+        <v>-0.5377999999999999</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.918</v>
+        <v>-0.9359</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.6065</v>
+        <v>-1.6378</v>
       </c>
       <c r="R19" t="n">
-        <v>0.6885</v>
+        <v>0.7019</v>
       </c>
       <c r="S19" t="n">
-        <v>0.7745</v>
+        <v>0.7715</v>
       </c>
       <c r="T19" t="n">
-        <v>1.2727</v>
+        <v>1.1917</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.4981</v>
+        <v>-0.4202</v>
       </c>
       <c r="V19" t="n">
-        <v>0.2289</v>
+        <v>0.2139</v>
       </c>
       <c r="W19" t="n">
-        <v>0.3017</v>
+        <v>0.2686</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.0728</v>
+        <v>-0.0548</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
@@ -2060,58 +2060,58 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.6567</v>
+        <v>-2.6662</v>
       </c>
       <c r="E20" t="n">
-        <v>-3.9168</v>
+        <v>-3.9848</v>
       </c>
       <c r="F20" t="n">
-        <v>1.2601</v>
+        <v>1.3186</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.9837</v>
+        <v>-0.9714</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.2899</v>
+        <v>-0.2822</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.6939</v>
+        <v>-0.6891</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.5657</v>
+        <v>-1.5656</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.7573</v>
+        <v>-0.7579</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.8084</v>
+        <v>-0.8077</v>
       </c>
       <c r="M20" t="n">
-        <v>0.582</v>
+        <v>0.5942</v>
       </c>
       <c r="N20" t="n">
-        <v>0.4674</v>
+        <v>0.4756</v>
       </c>
       <c r="O20" t="n">
-        <v>0.1146</v>
+        <v>0.1186</v>
       </c>
       <c r="P20" t="n">
-        <v>-1.836</v>
+        <v>-1.8718</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.295</v>
+        <v>-2.3397</v>
       </c>
       <c r="R20" t="n">
-        <v>0.459</v>
+        <v>0.4679</v>
       </c>
       <c r="S20" t="n">
-        <v>0.163</v>
+        <v>0.1769</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.0561</v>
+        <v>-0.0795</v>
       </c>
       <c r="U20" t="n">
-        <v>0.2191</v>
+        <v>0.2564</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2143,67 +2143,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.3401</v>
+        <v>-3.3698</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.9036</v>
+        <v>-3.0465</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.4365</v>
+        <v>-0.3232</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.5702</v>
+        <v>-2.5306</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.6232</v>
+        <v>-0.5946</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.9469</v>
+        <v>-1.936</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.6732</v>
+        <v>-1.6812</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.7232</v>
+        <v>-0.7247</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.95</v>
+        <v>-0.9565</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.897</v>
+        <v>-0.8494</v>
       </c>
       <c r="N21" t="n">
-        <v>0.1</v>
+        <v>0.1301</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.9969</v>
+        <v>-0.9795</v>
       </c>
       <c r="P21" t="n">
-        <v>-1.377</v>
+        <v>-1.4038</v>
       </c>
       <c r="Q21" t="n">
-        <v>-2.5244</v>
+        <v>-2.5737</v>
       </c>
       <c r="R21" t="n">
-        <v>1.1475</v>
+        <v>1.1699</v>
       </c>
       <c r="S21" t="n">
-        <v>0.3781</v>
+        <v>0.3508</v>
       </c>
       <c r="T21" t="n">
-        <v>0.9923</v>
+        <v>0.9398</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.6142</v>
+        <v>-0.589</v>
       </c>
       <c r="V21" t="n">
-        <v>0.2289</v>
+        <v>0.2139</v>
       </c>
       <c r="W21" t="n">
-        <v>0.3017</v>
+        <v>0.2686</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.0728</v>
+        <v>-0.0548</v>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
@@ -2214,7 +2214,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>T. FORREST</t>
+          <t>T. LUWAWU-CABARROT</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2226,67 +2226,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.9791</v>
+        <v>-3.984</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.3116</v>
+        <v>-3.6315</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.6676</v>
+        <v>-0.3526</v>
       </c>
       <c r="G22" t="n">
-        <v>1.5915</v>
+        <v>-4.3002</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.1969</v>
+        <v>-1.8595</v>
       </c>
       <c r="I22" t="n">
-        <v>1.7885</v>
+        <v>-2.4406</v>
       </c>
       <c r="J22" t="n">
-        <v>2.0713</v>
+        <v>-2.8149</v>
       </c>
       <c r="K22" t="n">
-        <v>-1.0172</v>
+        <v>-2.2903</v>
       </c>
       <c r="L22" t="n">
-        <v>3.0885</v>
+        <v>-0.5246</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.4797</v>
+        <v>-1.4853</v>
       </c>
       <c r="N22" t="n">
-        <v>0.8203</v>
+        <v>0.4307</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.3</v>
+        <v>-1.916</v>
       </c>
       <c r="P22" t="n">
-        <v>-4.1309</v>
+        <v>-1.1699</v>
       </c>
       <c r="Q22" t="n">
-        <v>-5.0489</v>
+        <v>-2.8077</v>
       </c>
       <c r="R22" t="n">
-        <v>0.918</v>
+        <v>1.6378</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.0456</v>
+        <v>1.4064</v>
       </c>
       <c r="T22" t="n">
-        <v>1.0562</v>
+        <v>1.9911</v>
       </c>
       <c r="U22" t="n">
-        <v>-1.1018</v>
+        <v>-0.5847</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.3941</v>
+        <v>0.0796</v>
       </c>
       <c r="W22" t="n">
-        <v>-0.3901</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.004</v>
+        <v>0.0796</v>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
@@ -2297,7 +2297,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>T. LUWAWU-CABARROT</t>
+          <t>T. FORREST</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2309,67 +2309,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.9848</v>
+        <v>-4.0756</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.4602</v>
+        <v>-2.6183</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.5245</v>
+        <v>-1.4573</v>
       </c>
       <c r="G23" t="n">
-        <v>-4.3418</v>
+        <v>1.5838</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.9097</v>
+        <v>-0.1795</v>
       </c>
       <c r="I23" t="n">
-        <v>-2.4322</v>
+        <v>1.7633</v>
       </c>
       <c r="J23" t="n">
-        <v>-2.7743</v>
+        <v>1.9608</v>
       </c>
       <c r="K23" t="n">
-        <v>-2.2889</v>
+        <v>-1.0724</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.4854</v>
+        <v>3.0332</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.5675</v>
+        <v>-0.377</v>
       </c>
       <c r="N23" t="n">
-        <v>0.3793</v>
+        <v>0.8929</v>
       </c>
       <c r="O23" t="n">
-        <v>-1.9468</v>
+        <v>-1.2699</v>
       </c>
       <c r="P23" t="n">
-        <v>-1.1475</v>
+        <v>-4.2115</v>
       </c>
       <c r="Q23" t="n">
-        <v>-2.7539</v>
+        <v>-5.1474</v>
       </c>
       <c r="R23" t="n">
-        <v>1.6065</v>
+        <v>0.9359</v>
       </c>
       <c r="S23" t="n">
-        <v>1.4265</v>
+        <v>-0.0655</v>
       </c>
       <c r="T23" t="n">
-        <v>2.0681</v>
+        <v>0.9661</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.6415</v>
+        <v>-1.0316</v>
       </c>
       <c r="V23" t="n">
-        <v>0.078</v>
+        <v>-1.3823</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>-0.3978</v>
       </c>
       <c r="X23" t="n">
-        <v>0.078</v>
+        <v>-0.9846</v>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
@@ -2392,67 +2392,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.4103</v>
+        <v>-4.3769</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.1897</v>
+        <v>-3.276</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.2206</v>
+        <v>-1.1009</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.9367</v>
+        <v>-0.904</v>
       </c>
       <c r="H24" t="n">
-        <v>-1.4487</v>
+        <v>-1.4189</v>
       </c>
       <c r="I24" t="n">
-        <v>0.512</v>
+        <v>0.5149</v>
       </c>
       <c r="J24" t="n">
-        <v>-1.4746</v>
+        <v>-1.4758</v>
       </c>
       <c r="K24" t="n">
-        <v>-1.5487</v>
+        <v>-1.549</v>
       </c>
       <c r="L24" t="n">
-        <v>0.0741</v>
+        <v>0.0732</v>
       </c>
       <c r="M24" t="n">
-        <v>0.5379</v>
+        <v>0.5718</v>
       </c>
       <c r="N24" t="n">
-        <v>0.1</v>
+        <v>0.1301</v>
       </c>
       <c r="O24" t="n">
-        <v>0.4379</v>
+        <v>0.4417</v>
       </c>
       <c r="P24" t="n">
-        <v>-1.377</v>
+        <v>-1.4038</v>
       </c>
       <c r="Q24" t="n">
-        <v>-1.377</v>
+        <v>-1.4038</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.0835</v>
+        <v>-0.0752</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.489</v>
+        <v>-0.5306999999999999</v>
       </c>
       <c r="U24" t="n">
-        <v>0.4055</v>
+        <v>0.4556</v>
       </c>
       <c r="V24" t="n">
-        <v>-2.0132</v>
+        <v>-1.9939</v>
       </c>
       <c r="W24" t="n">
-        <v>0.1509</v>
+        <v>0.1343</v>
       </c>
       <c r="X24" t="n">
-        <v>-2.164</v>
+        <v>-2.1282</v>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
@@ -2475,67 +2475,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-20.1162</v>
+        <v>-20.2371</v>
       </c>
       <c r="E25" t="n">
-        <v>-17.2285</v>
+        <v>-18.876</v>
       </c>
       <c r="F25" t="n">
-        <v>-2.887799999999999</v>
+        <v>-1.3611</v>
       </c>
       <c r="G25" t="n">
-        <v>-9.437099999999999</v>
+        <v>-9.2567</v>
       </c>
       <c r="H25" t="n">
-        <v>-1.9254</v>
+        <v>-1.7726</v>
       </c>
       <c r="I25" t="n">
-        <v>-7.511699999999999</v>
+        <v>-7.4839</v>
       </c>
       <c r="J25" t="n">
-        <v>-7.1993</v>
+        <v>-7.660100000000002</v>
       </c>
       <c r="K25" t="n">
-        <v>-5.8504</v>
+        <v>-6.147499999999999</v>
       </c>
       <c r="L25" t="n">
-        <v>-1.3486</v>
+        <v>-1.5126</v>
       </c>
       <c r="M25" t="n">
-        <v>-2.2378</v>
+        <v>-1.5964</v>
       </c>
       <c r="N25" t="n">
-        <v>3.9251</v>
+        <v>4.3746</v>
       </c>
       <c r="O25" t="n">
-        <v>-6.1628</v>
+        <v>-5.971099999999999</v>
       </c>
       <c r="P25" t="n">
-        <v>-12.6224</v>
+        <v>-12.8684</v>
       </c>
       <c r="Q25" t="n">
-        <v>-20.6545</v>
+        <v>-21.0575</v>
       </c>
       <c r="R25" t="n">
-        <v>8.032500000000001</v>
+        <v>8.1891</v>
       </c>
       <c r="S25" t="n">
-        <v>3.0251</v>
+        <v>2.952</v>
       </c>
       <c r="T25" t="n">
-        <v>7.015299999999999</v>
+        <v>6.375400000000001</v>
       </c>
       <c r="U25" t="n">
-        <v>-3.9901</v>
+        <v>-3.4234</v>
       </c>
       <c r="V25" t="n">
-        <v>-1.082</v>
+        <v>-1.063900000000001</v>
       </c>
       <c r="W25" t="n">
-        <v>3.610200000000001</v>
+        <v>3.4661</v>
       </c>
       <c r="X25" t="n">
-        <v>-4.692200000000001</v>
+        <v>-4.5303</v>
       </c>
       <c r="Y25" t="inlineStr"/>
     </row>

--- a/informes_data/ACB/2025-26/playoffs/individual/NP_play_by_play_105353_W2.xlsx
+++ b/informes_data/ACB/2025-26/playoffs/individual/NP_play_by_play_105353_W2.xlsx
@@ -570,64 +570,64 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>10.3213</v>
+        <v>10.3694</v>
       </c>
       <c r="E2" t="n">
-        <v>8.7193</v>
+        <v>8.8466</v>
       </c>
       <c r="F2" t="n">
-        <v>1.602</v>
+        <v>1.5228</v>
       </c>
       <c r="G2" t="n">
-        <v>7.3612</v>
+        <v>7.3945</v>
       </c>
       <c r="H2" t="n">
-        <v>-1.8285</v>
+        <v>-1.8474</v>
       </c>
       <c r="I2" t="n">
-        <v>9.1897</v>
+        <v>9.241899999999999</v>
       </c>
       <c r="J2" t="n">
-        <v>7.5882</v>
+        <v>7.6089</v>
       </c>
       <c r="K2" t="n">
-        <v>-2.1067</v>
+        <v>-2.1274</v>
       </c>
       <c r="L2" t="n">
-        <v>9.694900000000001</v>
+        <v>9.7363</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.227</v>
+        <v>-0.2143</v>
       </c>
       <c r="N2" t="n">
-        <v>0.2782</v>
+        <v>0.28</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.5051</v>
+        <v>-0.4943</v>
       </c>
       <c r="P2" t="n">
-        <v>1.1699</v>
+        <v>1.1604</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.1699</v>
+        <v>-1.1604</v>
       </c>
       <c r="R2" t="n">
-        <v>2.3397</v>
+        <v>2.3207</v>
       </c>
       <c r="S2" t="n">
-        <v>0.5918</v>
+        <v>0.6015</v>
       </c>
       <c r="T2" t="n">
-        <v>1.1026</v>
+        <v>1.1851</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.5108</v>
+        <v>-0.5836</v>
       </c>
       <c r="V2" t="n">
-        <v>1.1984</v>
+        <v>1.213</v>
       </c>
       <c r="W2" t="n">
-        <v>1.1984</v>
+        <v>1.213</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
@@ -653,64 +653,64 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.8932</v>
+        <v>3.8983</v>
       </c>
       <c r="E3" t="n">
-        <v>0.6981000000000001</v>
+        <v>0.7811</v>
       </c>
       <c r="F3" t="n">
-        <v>3.1951</v>
+        <v>3.1173</v>
       </c>
       <c r="G3" t="n">
-        <v>1.1147</v>
+        <v>1.1269</v>
       </c>
       <c r="H3" t="n">
-        <v>1.3646</v>
+        <v>1.3798</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.2499</v>
+        <v>-0.253</v>
       </c>
       <c r="J3" t="n">
-        <v>0.073</v>
+        <v>0.0648</v>
       </c>
       <c r="K3" t="n">
-        <v>0.5928</v>
+        <v>0.6007</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.5197000000000001</v>
+        <v>-0.5359</v>
       </c>
       <c r="M3" t="n">
-        <v>1.0416</v>
+        <v>1.0621</v>
       </c>
       <c r="N3" t="n">
-        <v>0.7718</v>
+        <v>0.7791</v>
       </c>
       <c r="O3" t="n">
-        <v>0.2699</v>
+        <v>0.2829</v>
       </c>
       <c r="P3" t="n">
-        <v>1.6378</v>
+        <v>1.6245</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.1699</v>
+        <v>-1.1604</v>
       </c>
       <c r="R3" t="n">
-        <v>2.8077</v>
+        <v>2.7849</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0766</v>
+        <v>0.0752</v>
       </c>
       <c r="T3" t="n">
-        <v>0.7308</v>
+        <v>0.8048999999999999</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.6542</v>
+        <v>-0.7297</v>
       </c>
       <c r="V3" t="n">
-        <v>1.0641</v>
+        <v>1.0717</v>
       </c>
       <c r="W3" t="n">
-        <v>1.0641</v>
+        <v>1.0717</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
@@ -736,67 +736,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.3655</v>
+        <v>3.3483</v>
       </c>
       <c r="E4" t="n">
-        <v>1.6354</v>
+        <v>1.6837</v>
       </c>
       <c r="F4" t="n">
-        <v>1.7301</v>
+        <v>1.6645</v>
       </c>
       <c r="G4" t="n">
-        <v>1.2213</v>
+        <v>1.2418</v>
       </c>
       <c r="H4" t="n">
-        <v>0.6157</v>
+        <v>0.6232</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6056</v>
+        <v>0.6186</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.0383</v>
+        <v>-0.0389</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.3311</v>
+        <v>-0.3332</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2928</v>
+        <v>0.2943</v>
       </c>
       <c r="M4" t="n">
-        <v>1.2596</v>
+        <v>1.2807</v>
       </c>
       <c r="N4" t="n">
-        <v>0.9468</v>
+        <v>0.9564</v>
       </c>
       <c r="O4" t="n">
-        <v>0.3128</v>
+        <v>0.3243</v>
       </c>
       <c r="P4" t="n">
-        <v>1.8718</v>
+        <v>1.8566</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.8718</v>
+        <v>1.8566</v>
       </c>
       <c r="S4" t="n">
-        <v>0.4067</v>
+        <v>0.3912</v>
       </c>
       <c r="T4" t="n">
-        <v>1.6737</v>
+        <v>1.7226</v>
       </c>
       <c r="U4" t="n">
-        <v>-1.267</v>
+        <v>-1.3314</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.1343</v>
+        <v>-0.1413</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.1343</v>
+        <v>-0.1413</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
@@ -819,64 +819,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.0441</v>
+        <v>3.0659</v>
       </c>
       <c r="E5" t="n">
-        <v>2.1919</v>
+        <v>2.2496</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8522</v>
+        <v>0.8163</v>
       </c>
       <c r="G5" t="n">
-        <v>1.9057</v>
+        <v>1.9339</v>
       </c>
       <c r="H5" t="n">
-        <v>2.5191</v>
+        <v>2.5479</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.6135</v>
+        <v>-0.614</v>
       </c>
       <c r="J5" t="n">
-        <v>2.048</v>
+        <v>2.072</v>
       </c>
       <c r="K5" t="n">
-        <v>2.048</v>
+        <v>2.072</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.1423</v>
+        <v>-0.1381</v>
       </c>
       <c r="N5" t="n">
-        <v>0.4711</v>
+        <v>0.4759</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.6135</v>
+        <v>-0.614</v>
       </c>
       <c r="P5" t="n">
-        <v>1.1699</v>
+        <v>1.1604</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.1699</v>
+        <v>1.1604</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.1657</v>
+        <v>-0.1697</v>
       </c>
       <c r="T5" t="n">
-        <v>0.009599999999999999</v>
+        <v>0.0362</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.1753</v>
+        <v>-0.2059</v>
       </c>
       <c r="V5" t="n">
-        <v>0.1343</v>
+        <v>0.1413</v>
       </c>
       <c r="W5" t="n">
-        <v>0.1343</v>
+        <v>0.1413</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -902,67 +902,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.9137</v>
+        <v>1.9027</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1285</v>
+        <v>0.2042</v>
       </c>
       <c r="F6" t="n">
-        <v>1.7852</v>
+        <v>1.6986</v>
       </c>
       <c r="G6" t="n">
-        <v>1.0608</v>
+        <v>1.071</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.3047</v>
+        <v>-0.3088</v>
       </c>
       <c r="I6" t="n">
-        <v>1.3655</v>
+        <v>1.3798</v>
       </c>
       <c r="J6" t="n">
-        <v>0.5794</v>
+        <v>0.5793</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.5919</v>
+        <v>-0.5981</v>
       </c>
       <c r="L6" t="n">
-        <v>1.1713</v>
+        <v>1.1774</v>
       </c>
       <c r="M6" t="n">
-        <v>0.4814</v>
+        <v>0.4917</v>
       </c>
       <c r="N6" t="n">
-        <v>0.2872</v>
+        <v>0.2893</v>
       </c>
       <c r="O6" t="n">
-        <v>0.1942</v>
+        <v>0.2024</v>
       </c>
       <c r="P6" t="n">
-        <v>0.7019</v>
+        <v>0.6962</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.1699</v>
+        <v>-1.1604</v>
       </c>
       <c r="R6" t="n">
-        <v>1.8718</v>
+        <v>1.8566</v>
       </c>
       <c r="S6" t="n">
-        <v>1.0808</v>
+        <v>1.0659</v>
       </c>
       <c r="T6" t="n">
-        <v>0.5847</v>
+        <v>0.6439</v>
       </c>
       <c r="U6" t="n">
-        <v>0.4961</v>
+        <v>0.422</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.9298</v>
+        <v>-0.9304</v>
       </c>
       <c r="W6" t="n">
-        <v>0.1343</v>
+        <v>0.1413</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.0641</v>
+        <v>-1.0717</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -985,67 +985,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.8037</v>
+        <v>0.7633</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.038</v>
+        <v>-2.0175</v>
       </c>
       <c r="F7" t="n">
-        <v>2.8418</v>
+        <v>2.7808</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.8397</v>
+        <v>-0.8433</v>
       </c>
       <c r="H7" t="n">
-        <v>0.2369</v>
+        <v>0.2398</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.0766</v>
+        <v>-1.0831</v>
       </c>
       <c r="J7" t="n">
-        <v>-2.1512</v>
+        <v>-2.1747</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.7188</v>
+        <v>-0.7259</v>
       </c>
       <c r="L7" t="n">
-        <v>-1.4324</v>
+        <v>-1.4488</v>
       </c>
       <c r="M7" t="n">
-        <v>1.3115</v>
+        <v>1.3314</v>
       </c>
       <c r="N7" t="n">
-        <v>0.9558</v>
+        <v>0.9657</v>
       </c>
       <c r="O7" t="n">
-        <v>0.3558</v>
+        <v>0.3657</v>
       </c>
       <c r="P7" t="n">
-        <v>1.4038</v>
+        <v>1.3924</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.4038</v>
+        <v>1.3924</v>
       </c>
       <c r="S7" t="n">
-        <v>0.7716</v>
+        <v>0.7501</v>
       </c>
       <c r="T7" t="n">
-        <v>0.5109</v>
+        <v>0.5517</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2607</v>
+        <v>0.1984</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.5321</v>
+        <v>-0.5359</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.3978</v>
+        <v>-0.3945</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.1343</v>
+        <v>-0.1413</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1068,58 +1068,58 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6257</v>
+        <v>0.63</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.8433</v>
+        <v>-0.7791</v>
       </c>
       <c r="F8" t="n">
-        <v>1.469</v>
+        <v>1.4091</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.519</v>
+        <v>-0.5237000000000001</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.7015</v>
+        <v>-1.7195</v>
       </c>
       <c r="I8" t="n">
-        <v>1.1825</v>
+        <v>1.1958</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.7914</v>
+        <v>-0.8061</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.3381</v>
+        <v>-1.3511</v>
       </c>
       <c r="L8" t="n">
-        <v>0.5466</v>
+        <v>0.545</v>
       </c>
       <c r="M8" t="n">
-        <v>0.2724</v>
+        <v>0.2824</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.3635</v>
+        <v>-0.3684</v>
       </c>
       <c r="O8" t="n">
-        <v>0.6359</v>
+        <v>0.6508</v>
       </c>
       <c r="P8" t="n">
-        <v>0.4679</v>
+        <v>0.4641</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.1699</v>
+        <v>-1.1604</v>
       </c>
       <c r="R8" t="n">
-        <v>1.6378</v>
+        <v>1.6245</v>
       </c>
       <c r="S8" t="n">
-        <v>0.6768</v>
+        <v>0.6896</v>
       </c>
       <c r="T8" t="n">
-        <v>1.118</v>
+        <v>1.1874</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.4412</v>
+        <v>-0.4978</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1151,67 +1151,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.5917</v>
+        <v>0.5601</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.8357</v>
+        <v>-1.7974</v>
       </c>
       <c r="F9" t="n">
-        <v>2.4273</v>
+        <v>2.3575</v>
       </c>
       <c r="G9" t="n">
-        <v>0.5726</v>
+        <v>0.5829</v>
       </c>
       <c r="H9" t="n">
-        <v>0.7835</v>
+        <v>0.7921</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.2108</v>
+        <v>-0.2092</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.4498</v>
+        <v>-0.454</v>
       </c>
       <c r="K9" t="n">
-        <v>0.3213</v>
+        <v>0.3255</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.7711</v>
+        <v>-0.7796</v>
       </c>
       <c r="M9" t="n">
-        <v>1.0224</v>
+        <v>1.0369</v>
       </c>
       <c r="N9" t="n">
-        <v>0.4622</v>
+        <v>0.4665</v>
       </c>
       <c r="O9" t="n">
-        <v>0.5603</v>
+        <v>0.5703</v>
       </c>
       <c r="P9" t="n">
-        <v>0.9359</v>
+        <v>0.9283</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.1699</v>
+        <v>-1.1604</v>
       </c>
       <c r="R9" t="n">
-        <v>2.1057</v>
+        <v>2.0886</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.7825</v>
+        <v>-0.8097</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.216</v>
+        <v>-0.183</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.5665</v>
+        <v>-0.6267</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.1343</v>
+        <v>-0.1413</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.1343</v>
+        <v>-0.1413</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1234,67 +1234,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.435</v>
+        <v>0.3931</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.7236</v>
+        <v>-0.7178</v>
       </c>
       <c r="F10" t="n">
-        <v>1.1586</v>
+        <v>1.1109</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.0403</v>
+        <v>-0.0367</v>
       </c>
       <c r="H10" t="n">
-        <v>0.8167</v>
+        <v>0.8257</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.857</v>
+        <v>-0.8623</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.7486</v>
+        <v>-0.7563</v>
       </c>
       <c r="K10" t="n">
-        <v>0.0224</v>
+        <v>0.0233</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.7711</v>
+        <v>-0.7796</v>
       </c>
       <c r="M10" t="n">
-        <v>0.7083</v>
+        <v>0.7196</v>
       </c>
       <c r="N10" t="n">
-        <v>0.7942</v>
+        <v>0.8024</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.0859</v>
+        <v>-0.0828</v>
       </c>
       <c r="P10" t="n">
-        <v>1.1699</v>
+        <v>1.1604</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.1699</v>
+        <v>1.1604</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.958</v>
+        <v>-0.9838</v>
       </c>
       <c r="T10" t="n">
-        <v>0.025</v>
+        <v>0.0385</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.983</v>
+        <v>-1.0223</v>
       </c>
       <c r="V10" t="n">
-        <v>0.2634</v>
+        <v>0.2532</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0.2634</v>
+        <v>0.2532</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1317,67 +1317,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.4399</v>
+        <v>-1.4837</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.4379</v>
+        <v>-2.4155</v>
       </c>
       <c r="F11" t="n">
-        <v>0.998</v>
+        <v>0.9318</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.8341</v>
+        <v>-0.8399</v>
       </c>
       <c r="H11" t="n">
-        <v>0.346</v>
+        <v>0.349</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.1801</v>
+        <v>-1.1889</v>
       </c>
       <c r="J11" t="n">
-        <v>-2.0046</v>
+        <v>-2.0261</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.4258</v>
+        <v>-0.4301</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.5788</v>
+        <v>-1.5959</v>
       </c>
       <c r="M11" t="n">
-        <v>1.1705</v>
+        <v>1.1862</v>
       </c>
       <c r="N11" t="n">
-        <v>0.7718</v>
+        <v>0.7791</v>
       </c>
       <c r="O11" t="n">
-        <v>0.3987</v>
+        <v>0.4071</v>
       </c>
       <c r="P11" t="n">
-        <v>1.8718</v>
+        <v>1.8566</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.8718</v>
+        <v>1.8566</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.4135</v>
+        <v>-1.4286</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.4333</v>
+        <v>-0.3894</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.9802</v>
+        <v>-1.0392</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.0641</v>
+        <v>-1.0717</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.0641</v>
+        <v>-1.0717</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1400,67 +1400,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.7848</v>
+        <v>-1.8075</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.3972</v>
+        <v>-3.3217</v>
       </c>
       <c r="F12" t="n">
-        <v>1.6124</v>
+        <v>1.5142</v>
       </c>
       <c r="G12" t="n">
-        <v>-1.7467</v>
+        <v>-1.7575</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.0751</v>
+        <v>-1.0861</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.6715</v>
+        <v>-0.6714</v>
       </c>
       <c r="J12" t="n">
-        <v>-2.5082</v>
+        <v>-2.5344</v>
       </c>
       <c r="K12" t="n">
-        <v>-1.8469</v>
+        <v>-1.8652</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.6613</v>
+        <v>-0.6692</v>
       </c>
       <c r="M12" t="n">
-        <v>0.7615</v>
+        <v>0.7769</v>
       </c>
       <c r="N12" t="n">
-        <v>0.7718</v>
+        <v>0.7791</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.0103</v>
+        <v>-0.0022</v>
       </c>
       <c r="P12" t="n">
-        <v>0.4679</v>
+        <v>0.4641</v>
       </c>
       <c r="Q12" t="n">
-        <v>-2.3397</v>
+        <v>-2.3207</v>
       </c>
       <c r="R12" t="n">
-        <v>2.8077</v>
+        <v>2.7849</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.7045</v>
+        <v>-1.7272</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.1506</v>
+        <v>-0.1037</v>
       </c>
       <c r="U12" t="n">
-        <v>-1.5539</v>
+        <v>-1.6235</v>
       </c>
       <c r="V12" t="n">
-        <v>1.1984</v>
+        <v>1.213</v>
       </c>
       <c r="W12" t="n">
-        <v>1.6013</v>
+        <v>1.6371</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.4029</v>
+        <v>-0.424</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1483,67 +1483,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>21.76919999999999</v>
+        <v>21.6399</v>
       </c>
       <c r="E13" t="n">
-        <v>2.097500000000001</v>
+        <v>2.716199999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>19.6717</v>
+        <v>18.9238</v>
       </c>
       <c r="G13" t="n">
-        <v>9.256499999999997</v>
+        <v>9.349899999999998</v>
       </c>
       <c r="H13" t="n">
-        <v>1.772699999999999</v>
+        <v>1.7957</v>
       </c>
       <c r="I13" t="n">
-        <v>7.483900000000002</v>
+        <v>7.5542</v>
       </c>
       <c r="J13" t="n">
-        <v>1.5965</v>
+        <v>1.534500000000001</v>
       </c>
       <c r="K13" t="n">
-        <v>-4.3748</v>
+        <v>-4.4095</v>
       </c>
       <c r="L13" t="n">
-        <v>5.9712</v>
+        <v>5.943999999999999</v>
       </c>
       <c r="M13" t="n">
-        <v>7.6599</v>
+        <v>7.815499999999999</v>
       </c>
       <c r="N13" t="n">
-        <v>6.147399999999999</v>
+        <v>6.2051</v>
       </c>
       <c r="O13" t="n">
-        <v>1.5128</v>
+        <v>1.6102</v>
       </c>
       <c r="P13" t="n">
-        <v>12.8685</v>
+        <v>12.764</v>
       </c>
       <c r="Q13" t="n">
-        <v>-8.1892</v>
+        <v>-8.1227</v>
       </c>
       <c r="R13" t="n">
-        <v>21.0576</v>
+        <v>20.8866</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.4199</v>
+        <v>-1.5455</v>
       </c>
       <c r="T13" t="n">
-        <v>4.955400000000001</v>
+        <v>5.4942</v>
       </c>
       <c r="U13" t="n">
-        <v>-6.375300000000001</v>
+        <v>-7.039700000000001</v>
       </c>
       <c r="V13" t="n">
-        <v>1.064</v>
+        <v>1.0716</v>
       </c>
       <c r="W13" t="n">
-        <v>3.7346</v>
+        <v>3.8099</v>
       </c>
       <c r="X13" t="n">
-        <v>-2.6706</v>
+        <v>-2.7381</v>
       </c>
       <c r="Y13" t="inlineStr"/>
     </row>
@@ -1562,64 +1562,64 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.0339</v>
+        <v>2.0841</v>
       </c>
       <c r="E14" t="n">
-        <v>1.4199</v>
+        <v>1.5389</v>
       </c>
       <c r="F14" t="n">
-        <v>0.614</v>
+        <v>0.5453</v>
       </c>
       <c r="G14" t="n">
-        <v>2.1063</v>
+        <v>2.1372</v>
       </c>
       <c r="H14" t="n">
-        <v>3.3874</v>
+        <v>3.4249</v>
       </c>
       <c r="I14" t="n">
-        <v>-1.2811</v>
+        <v>-1.2877</v>
       </c>
       <c r="J14" t="n">
-        <v>2.2948</v>
+        <v>2.3148</v>
       </c>
       <c r="K14" t="n">
-        <v>2.6291</v>
+        <v>2.6598</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.3343</v>
+        <v>-0.345</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.1885</v>
+        <v>-0.1776</v>
       </c>
       <c r="N14" t="n">
-        <v>0.7583</v>
+        <v>0.7652</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.9468</v>
+        <v>-0.9428</v>
       </c>
       <c r="P14" t="n">
-        <v>-1.4038</v>
+        <v>-1.3924</v>
       </c>
       <c r="Q14" t="n">
-        <v>-2.5737</v>
+        <v>-2.5528</v>
       </c>
       <c r="R14" t="n">
-        <v>1.1699</v>
+        <v>1.1604</v>
       </c>
       <c r="S14" t="n">
-        <v>0.7994</v>
+        <v>0.8035</v>
       </c>
       <c r="T14" t="n">
-        <v>1.1667</v>
+        <v>1.241</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.3674</v>
+        <v>-0.4375</v>
       </c>
       <c r="V14" t="n">
-        <v>0.5321</v>
+        <v>0.5359</v>
       </c>
       <c r="W14" t="n">
-        <v>0.5321</v>
+        <v>0.5359</v>
       </c>
       <c r="X14" t="n">
         <v>0</v>
@@ -1645,67 +1645,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.183</v>
+        <v>0.202</v>
       </c>
       <c r="E15" t="n">
-        <v>-1.6109</v>
+        <v>-1.5219</v>
       </c>
       <c r="F15" t="n">
-        <v>1.7939</v>
+        <v>1.724</v>
       </c>
       <c r="G15" t="n">
-        <v>0.5935</v>
+        <v>0.6028</v>
       </c>
       <c r="H15" t="n">
-        <v>1.6423</v>
+        <v>1.6607</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.0488</v>
+        <v>-1.0578</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.2109</v>
+        <v>-0.2154</v>
       </c>
       <c r="K15" t="n">
-        <v>0.709</v>
+        <v>0.7183</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.9199000000000001</v>
+        <v>-0.9337</v>
       </c>
       <c r="M15" t="n">
-        <v>0.8045</v>
+        <v>0.8183</v>
       </c>
       <c r="N15" t="n">
-        <v>0.9333</v>
+        <v>0.9424</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.1289</v>
+        <v>-0.1241</v>
       </c>
       <c r="P15" t="n">
-        <v>-1.6378</v>
+        <v>-1.6245</v>
       </c>
       <c r="Q15" t="n">
-        <v>-2.5737</v>
+        <v>-2.5528</v>
       </c>
       <c r="R15" t="n">
-        <v>0.9359</v>
+        <v>0.9283</v>
       </c>
       <c r="S15" t="n">
-        <v>0.8843</v>
+        <v>0.8915999999999999</v>
       </c>
       <c r="T15" t="n">
-        <v>0.6417</v>
+        <v>0.7104</v>
       </c>
       <c r="U15" t="n">
-        <v>0.2426</v>
+        <v>0.1812</v>
       </c>
       <c r="V15" t="n">
-        <v>0.343</v>
+        <v>0.3321</v>
       </c>
       <c r="W15" t="n">
-        <v>0.5321</v>
+        <v>0.5359</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.1891</v>
+        <v>-0.2038</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
@@ -1728,40 +1728,40 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.4273</v>
+        <v>-0.424</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.3648</v>
+        <v>-0.3424</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.0625</v>
+        <v>-0.08160000000000001</v>
       </c>
       <c r="G16" t="n">
-        <v>0.0044</v>
+        <v>0.0057</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.1508</v>
+        <v>-0.153</v>
       </c>
       <c r="I16" t="n">
-        <v>0.1552</v>
+        <v>0.1587</v>
       </c>
       <c r="J16" t="n">
-        <v>0.0698</v>
+        <v>0.0704</v>
       </c>
       <c r="K16" t="n">
-        <v>0.0332</v>
+        <v>0.0336</v>
       </c>
       <c r="L16" t="n">
-        <v>0.0366</v>
+        <v>0.0368</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.0654</v>
+        <v>-0.06469999999999999</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.184</v>
+        <v>-0.1865</v>
       </c>
       <c r="O16" t="n">
-        <v>0.1186</v>
+        <v>0.1219</v>
       </c>
       <c r="P16" t="n">
         <v>0</v>
@@ -1773,13 +1773,13 @@
         <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.4317</v>
+        <v>-0.4297</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.4346</v>
+        <v>-0.4128</v>
       </c>
       <c r="U16" t="n">
-        <v>0.0029</v>
+        <v>-0.017</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1811,67 +1811,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.5446</v>
+        <v>-0.5695</v>
       </c>
       <c r="E17" t="n">
-        <v>0.523</v>
+        <v>0.5651</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.0676</v>
+        <v>-1.1346</v>
       </c>
       <c r="G17" t="n">
-        <v>-3.7515</v>
+        <v>-3.7877</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.7271</v>
+        <v>-1.7456</v>
       </c>
       <c r="I17" t="n">
-        <v>-2.0244</v>
+        <v>-2.042</v>
       </c>
       <c r="J17" t="n">
-        <v>-2.7553</v>
+        <v>-2.7937</v>
       </c>
       <c r="K17" t="n">
-        <v>-2.1624</v>
+        <v>-2.1843</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.5929</v>
+        <v>-0.6095</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.9962</v>
+        <v>-0.994</v>
       </c>
       <c r="N17" t="n">
-        <v>0.4352</v>
+        <v>0.4386</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.4314</v>
+        <v>-1.4326</v>
       </c>
       <c r="P17" t="n">
-        <v>0.9359</v>
+        <v>0.9283</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0.9359</v>
+        <v>0.9283</v>
       </c>
       <c r="S17" t="n">
-        <v>0.2771</v>
+        <v>0.2878</v>
       </c>
       <c r="T17" t="n">
-        <v>1.15</v>
+        <v>1.2154</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.8729</v>
+        <v>-0.9276</v>
       </c>
       <c r="V17" t="n">
-        <v>1.9939</v>
+        <v>2.0021</v>
       </c>
       <c r="W17" t="n">
-        <v>2.1282</v>
+        <v>2.1434</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.1343</v>
+        <v>-0.1413</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
@@ -1894,67 +1894,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.3977</v>
+        <v>-1.3946</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.5678</v>
+        <v>-0.5206</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.8299</v>
+        <v>-0.874</v>
       </c>
       <c r="G18" t="n">
-        <v>0.5744</v>
+        <v>0.5839</v>
       </c>
       <c r="H18" t="n">
-        <v>0.7852</v>
+        <v>0.7931</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.2108</v>
+        <v>-0.2092</v>
       </c>
       <c r="J18" t="n">
-        <v>0.059</v>
+        <v>0.0601</v>
       </c>
       <c r="K18" t="n">
-        <v>0.8300999999999999</v>
+        <v>0.8396</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.7711</v>
+        <v>-0.7796</v>
       </c>
       <c r="M18" t="n">
-        <v>0.5154</v>
+        <v>0.5238</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.0449</v>
+        <v>-0.0465</v>
       </c>
       <c r="O18" t="n">
-        <v>0.5603</v>
+        <v>0.5703</v>
       </c>
       <c r="P18" t="n">
-        <v>0.234</v>
+        <v>0.2321</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0.234</v>
+        <v>0.2321</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.142</v>
+        <v>-1.1388</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.6269</v>
+        <v>-0.5807</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.5151</v>
+        <v>-0.5581</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.0641</v>
+        <v>-1.0717</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.0641</v>
+        <v>-1.0717</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
@@ -1977,67 +1977,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.6119</v>
+        <v>-1.6068</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.7183</v>
+        <v>-1.6296</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1064</v>
+        <v>0.0228</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.6614</v>
+        <v>-1.6807</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.3749</v>
+        <v>-1.391</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.2865</v>
+        <v>-0.2898</v>
       </c>
       <c r="J19" t="n">
-        <v>-1.5408</v>
+        <v>-1.5673</v>
       </c>
       <c r="K19" t="n">
-        <v>-1.7922</v>
+        <v>-1.811</v>
       </c>
       <c r="L19" t="n">
-        <v>0.2514</v>
+        <v>0.2437</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.1205</v>
+        <v>-0.1134</v>
       </c>
       <c r="N19" t="n">
-        <v>0.4173</v>
+        <v>0.42</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.5377999999999999</v>
+        <v>-0.5335</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.9359</v>
+        <v>-0.9283</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.6378</v>
+        <v>-1.6245</v>
       </c>
       <c r="R19" t="n">
-        <v>0.7019</v>
+        <v>0.6962</v>
       </c>
       <c r="S19" t="n">
-        <v>0.7715</v>
+        <v>0.782</v>
       </c>
       <c r="T19" t="n">
-        <v>1.1917</v>
+        <v>1.2796</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.4202</v>
+        <v>-0.4976</v>
       </c>
       <c r="V19" t="n">
-        <v>0.2139</v>
+        <v>0.2202</v>
       </c>
       <c r="W19" t="n">
-        <v>0.2686</v>
+        <v>0.2827</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.0548</v>
+        <v>-0.0624</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
@@ -2060,58 +2060,58 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.6662</v>
+        <v>-2.671</v>
       </c>
       <c r="E20" t="n">
-        <v>-3.9848</v>
+        <v>-3.9613</v>
       </c>
       <c r="F20" t="n">
-        <v>1.3186</v>
+        <v>1.2904</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.9714</v>
+        <v>-0.98</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.2822</v>
+        <v>-0.2855</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.6891</v>
+        <v>-0.6945</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.5656</v>
+        <v>-1.5824</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.7579</v>
+        <v>-0.766</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.8077</v>
+        <v>-0.8164</v>
       </c>
       <c r="M20" t="n">
-        <v>0.5942</v>
+        <v>0.6024</v>
       </c>
       <c r="N20" t="n">
-        <v>0.4756</v>
+        <v>0.4805</v>
       </c>
       <c r="O20" t="n">
-        <v>0.1186</v>
+        <v>0.1219</v>
       </c>
       <c r="P20" t="n">
-        <v>-1.8718</v>
+        <v>-1.8566</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.3397</v>
+        <v>-2.3207</v>
       </c>
       <c r="R20" t="n">
-        <v>0.4679</v>
+        <v>0.4641</v>
       </c>
       <c r="S20" t="n">
-        <v>0.1769</v>
+        <v>0.1656</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.0795</v>
+        <v>-0.0583</v>
       </c>
       <c r="U20" t="n">
-        <v>0.2564</v>
+        <v>0.2238</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2143,67 +2143,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.3698</v>
+        <v>-3.3463</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.0465</v>
+        <v>-2.9746</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.3232</v>
+        <v>-0.3717</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.5306</v>
+        <v>-2.5541</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.5946</v>
+        <v>-0.6017</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.936</v>
+        <v>-1.9524</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.6812</v>
+        <v>-1.7029</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.7247</v>
+        <v>-0.7324000000000001</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.9565</v>
+        <v>-0.9705</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.8494</v>
+        <v>-0.8512</v>
       </c>
       <c r="N21" t="n">
-        <v>0.1301</v>
+        <v>0.1307</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.9795</v>
+        <v>-0.9819</v>
       </c>
       <c r="P21" t="n">
-        <v>-1.4038</v>
+        <v>-1.3924</v>
       </c>
       <c r="Q21" t="n">
-        <v>-2.5737</v>
+        <v>-2.5528</v>
       </c>
       <c r="R21" t="n">
-        <v>1.1699</v>
+        <v>1.1604</v>
       </c>
       <c r="S21" t="n">
-        <v>0.3508</v>
+        <v>0.38</v>
       </c>
       <c r="T21" t="n">
-        <v>0.9398</v>
+        <v>0.9984</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.589</v>
+        <v>-0.6185</v>
       </c>
       <c r="V21" t="n">
-        <v>0.2139</v>
+        <v>0.2202</v>
       </c>
       <c r="W21" t="n">
-        <v>0.2686</v>
+        <v>0.2827</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.0548</v>
+        <v>-0.0624</v>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
@@ -2226,67 +2226,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.984</v>
+        <v>-3.9952</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.6315</v>
+        <v>-3.5663</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.3526</v>
+        <v>-0.4289</v>
       </c>
       <c r="G22" t="n">
-        <v>-4.3002</v>
+        <v>-4.3529</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.8595</v>
+        <v>-1.8808</v>
       </c>
       <c r="I22" t="n">
-        <v>-2.4406</v>
+        <v>-2.4721</v>
       </c>
       <c r="J22" t="n">
-        <v>-2.8149</v>
+        <v>-2.8645</v>
       </c>
       <c r="K22" t="n">
-        <v>-2.2903</v>
+        <v>-2.3148</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.5246</v>
+        <v>-0.5497</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.4853</v>
+        <v>-1.4884</v>
       </c>
       <c r="N22" t="n">
-        <v>0.4307</v>
+        <v>0.434</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.916</v>
+        <v>-1.9224</v>
       </c>
       <c r="P22" t="n">
-        <v>-1.1699</v>
+        <v>-1.1604</v>
       </c>
       <c r="Q22" t="n">
-        <v>-2.8077</v>
+        <v>-2.7849</v>
       </c>
       <c r="R22" t="n">
-        <v>1.6378</v>
+        <v>1.6245</v>
       </c>
       <c r="S22" t="n">
-        <v>1.4064</v>
+        <v>1.4392</v>
       </c>
       <c r="T22" t="n">
-        <v>1.9911</v>
+        <v>2.0831</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.5847</v>
+        <v>-0.6439</v>
       </c>
       <c r="V22" t="n">
-        <v>0.0796</v>
+        <v>0.0789</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>0.0796</v>
+        <v>0.0789</v>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
@@ -2309,67 +2309,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.0756</v>
+        <v>-4.0233</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.6183</v>
+        <v>-2.4822</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.4573</v>
+        <v>-1.5411</v>
       </c>
       <c r="G23" t="n">
-        <v>1.5838</v>
+        <v>1.5888</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.1795</v>
+        <v>-0.1819</v>
       </c>
       <c r="I23" t="n">
-        <v>1.7633</v>
+        <v>1.7706</v>
       </c>
       <c r="J23" t="n">
-        <v>1.9608</v>
+        <v>1.9575</v>
       </c>
       <c r="K23" t="n">
-        <v>-1.0724</v>
+        <v>-1.0824</v>
       </c>
       <c r="L23" t="n">
-        <v>3.0332</v>
+        <v>3.04</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.377</v>
+        <v>-0.3688</v>
       </c>
       <c r="N23" t="n">
-        <v>0.8929</v>
+        <v>0.9005</v>
       </c>
       <c r="O23" t="n">
-        <v>-1.2699</v>
+        <v>-1.2693</v>
       </c>
       <c r="P23" t="n">
-        <v>-4.2115</v>
+        <v>-4.1773</v>
       </c>
       <c r="Q23" t="n">
-        <v>-5.1474</v>
+        <v>-5.1056</v>
       </c>
       <c r="R23" t="n">
-        <v>0.9359</v>
+        <v>0.9283</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.0655</v>
+        <v>-0.0475</v>
       </c>
       <c r="T23" t="n">
-        <v>0.9661</v>
+        <v>1.0603</v>
       </c>
       <c r="U23" t="n">
-        <v>-1.0316</v>
+        <v>-1.1078</v>
       </c>
       <c r="V23" t="n">
-        <v>-1.3823</v>
+        <v>-1.3873</v>
       </c>
       <c r="W23" t="n">
-        <v>-0.3978</v>
+        <v>-0.3945</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.9846</v>
+        <v>-0.9928</v>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
@@ -2392,67 +2392,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.3769</v>
+        <v>-4.3911</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.276</v>
+        <v>-3.2398</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.1009</v>
+        <v>-1.1513</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.904</v>
+        <v>-0.9127999999999999</v>
       </c>
       <c r="H24" t="n">
-        <v>-1.4189</v>
+        <v>-1.4349</v>
       </c>
       <c r="I24" t="n">
-        <v>0.5149</v>
+        <v>0.522</v>
       </c>
       <c r="J24" t="n">
-        <v>-1.4758</v>
+        <v>-1.492</v>
       </c>
       <c r="K24" t="n">
-        <v>-1.549</v>
+        <v>-1.5656</v>
       </c>
       <c r="L24" t="n">
-        <v>0.0732</v>
+        <v>0.0736</v>
       </c>
       <c r="M24" t="n">
-        <v>0.5718</v>
+        <v>0.5790999999999999</v>
       </c>
       <c r="N24" t="n">
-        <v>0.1301</v>
+        <v>0.1307</v>
       </c>
       <c r="O24" t="n">
-        <v>0.4417</v>
+        <v>0.4484</v>
       </c>
       <c r="P24" t="n">
-        <v>-1.4038</v>
+        <v>-1.3924</v>
       </c>
       <c r="Q24" t="n">
-        <v>-1.4038</v>
+        <v>-1.3924</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.0752</v>
+        <v>-0.0837</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.5306999999999999</v>
+        <v>-0.4967</v>
       </c>
       <c r="U24" t="n">
-        <v>0.4556</v>
+        <v>0.413</v>
       </c>
       <c r="V24" t="n">
-        <v>-1.9939</v>
+        <v>-2.0021</v>
       </c>
       <c r="W24" t="n">
-        <v>0.1343</v>
+        <v>0.1413</v>
       </c>
       <c r="X24" t="n">
-        <v>-2.1282</v>
+        <v>-2.1434</v>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
@@ -2475,67 +2475,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-20.2371</v>
+        <v>-20.1357</v>
       </c>
       <c r="E25" t="n">
-        <v>-18.876</v>
+        <v>-18.1347</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.3611</v>
+        <v>-2.0007</v>
       </c>
       <c r="G25" t="n">
-        <v>-9.2567</v>
+        <v>-9.349800000000002</v>
       </c>
       <c r="H25" t="n">
-        <v>-1.7726</v>
+        <v>-1.7957</v>
       </c>
       <c r="I25" t="n">
-        <v>-7.4839</v>
+        <v>-7.5542</v>
       </c>
       <c r="J25" t="n">
-        <v>-7.660100000000002</v>
+        <v>-7.815400000000001</v>
       </c>
       <c r="K25" t="n">
-        <v>-6.147499999999999</v>
+        <v>-6.2052</v>
       </c>
       <c r="L25" t="n">
-        <v>-1.5126</v>
+        <v>-1.6103</v>
       </c>
       <c r="M25" t="n">
-        <v>-1.5964</v>
+        <v>-1.5345</v>
       </c>
       <c r="N25" t="n">
-        <v>4.3746</v>
+        <v>4.4096</v>
       </c>
       <c r="O25" t="n">
-        <v>-5.971099999999999</v>
+        <v>-5.944100000000001</v>
       </c>
       <c r="P25" t="n">
-        <v>-12.8684</v>
+        <v>-12.7639</v>
       </c>
       <c r="Q25" t="n">
-        <v>-21.0575</v>
+        <v>-20.8865</v>
       </c>
       <c r="R25" t="n">
-        <v>8.1891</v>
+        <v>8.1226</v>
       </c>
       <c r="S25" t="n">
-        <v>2.952</v>
+        <v>3.05</v>
       </c>
       <c r="T25" t="n">
-        <v>6.375400000000001</v>
+        <v>7.0397</v>
       </c>
       <c r="U25" t="n">
-        <v>-3.4234</v>
+        <v>-3.99</v>
       </c>
       <c r="V25" t="n">
-        <v>-1.063900000000001</v>
+        <v>-1.071700000000001</v>
       </c>
       <c r="W25" t="n">
-        <v>3.4661</v>
+        <v>3.527400000000001</v>
       </c>
       <c r="X25" t="n">
-        <v>-4.5303</v>
+        <v>-4.5989</v>
       </c>
       <c r="Y25" t="inlineStr"/>
     </row>
